--- a/output2/【河洛話注音】金剛般若波羅蜜經004。妙行無住分第四.xlsx
+++ b/output2/【河洛話注音】金剛般若波羅蜜經004。妙行無住分第四.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9BD9031-3982-467E-9B7B-969F91BF59D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C84354-FA63-4153-B708-0E97BDD9B211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1725" yWindow="12495" windowWidth="36150" windowHeight="15585" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
+    <workbookView xWindow="-28545" yWindow="405" windowWidth="27645" windowHeight="15585" activeTab="1" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="10" r:id="rId1"/>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="364">
   <si>
     <t>【台羅拼音】</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1347,10 +1347,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㆠㄧㄠ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hang5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1367,38 +1363,18 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>tiu7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄧㄨ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hun1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄏㄨㄣ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>te7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄉㆤ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>si3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄙㄧ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hok8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1407,22 +1383,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>tshur3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄘ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>su1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄙㄨ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>phoo5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1447,14 +1411,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>u1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄨ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>huat4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1467,10 +1423,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄧㄣ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>soo2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1483,66 +1435,30 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄅㆦ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>si1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄙㄧ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ui7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄨㄧ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>m7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㆬ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>siek4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>siann1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄙ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>phang1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄆㄤ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>bi7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㆠㄧ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>tak4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1563,26 +1479,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄙㄧˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>siong3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄙㄧㆲ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ua5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄨㄚˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>i2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1595,10 +1495,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄍㆦ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>na2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1623,14 +1519,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>tiek4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>kho2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1655,10 +1543,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄧ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>un5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1671,58 +1555,26 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄉㄤ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hong1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄏㆲ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hi1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄏㄧ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>khong1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄎㆲ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ia7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄧㄚ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>se3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄙㆤ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tsun1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㄨㄣ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>lam5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1735,10 +1587,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄙㄞ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>pak4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1759,18 +1607,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄙㄧㄤ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>e7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㆤ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>iah8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1791,7 +1631,171 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄍㄚ˫</t>
+    <t>u5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄨˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tik4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄧㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zun1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆠㄧㄠ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zu7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗㄨ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄨㄣˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㆤ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cu3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄘㄨ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄨˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㄣ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄅㆦ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄨㄧ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆬ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sik4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㆩˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄆㄤˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆠㄧ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㆲ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ho5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄜˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㆦ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄤˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㆲˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄧˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄎㆲˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㄚ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㆤ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗㄨㄣˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄞˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㄤ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆤ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄚ˪</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1799,7 +1803,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="76">
+  <fonts count="77">
     <font>
       <sz val="16"/>
       <color rgb="FF000000"/>
@@ -2329,6 +2333,13 @@
       <color theme="1"/>
       <name val="細明體"/>
       <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="48"/>
+      <color rgb="FFFF0000"/>
+      <name val="Noto Serif TC Medium"/>
+      <family val="1"/>
       <charset val="136"/>
     </font>
   </fonts>
@@ -2531,7 +2542,7 @@
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2836,6 +2847,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3734,22 +3748,22 @@
         <v>250</v>
       </c>
       <c r="E4" s="89" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F4" s="89" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G4" s="89" t="s">
+        <v>329</v>
+      </c>
+      <c r="H4" s="89" t="s">
+        <v>255</v>
+      </c>
+      <c r="I4" s="89" t="s">
         <v>256</v>
       </c>
-      <c r="H4" s="89" t="s">
-        <v>258</v>
-      </c>
-      <c r="I4" s="89" t="s">
-        <v>260</v>
-      </c>
       <c r="J4" s="89" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="K4" s="89"/>
       <c r="L4" s="89"/>
@@ -3769,7 +3783,7 @@
       <c r="D5" s="72" t="s">
         <v>212</v>
       </c>
-      <c r="E5" s="72" t="s">
+      <c r="E5" s="105" t="s">
         <v>213</v>
       </c>
       <c r="F5" s="72" t="s">
@@ -3802,25 +3816,25 @@
       <c r="B6" s="67"/>
       <c r="C6" s="51"/>
       <c r="D6" s="94" t="s">
-        <v>251</v>
+        <v>328</v>
       </c>
       <c r="E6" s="94" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F6" s="94" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G6" s="94" t="s">
-        <v>257</v>
+        <v>330</v>
       </c>
       <c r="H6" s="94" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="I6" s="94" t="s">
-        <v>261</v>
+        <v>332</v>
       </c>
       <c r="J6" s="94" t="s">
-        <v>263</v>
+        <v>333</v>
       </c>
       <c r="K6" s="94"/>
       <c r="L6" s="94"/>
@@ -3858,41 +3872,41 @@
       <c r="B8" s="65"/>
       <c r="C8" s="52"/>
       <c r="D8" s="89" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="E8" s="89" t="s">
-        <v>266</v>
+        <v>334</v>
       </c>
       <c r="F8" s="89"/>
       <c r="G8" s="89"/>
       <c r="H8" s="89" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="I8" s="89" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="J8" s="89" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="K8" s="89"/>
       <c r="L8" s="89" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="M8" s="89" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="N8" s="89" t="s">
-        <v>276</v>
+        <v>322</v>
       </c>
       <c r="O8" s="89" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="P8" s="89"/>
       <c r="Q8" s="89" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="R8" s="89" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="S8" s="53"/>
       <c r="V8" s="100"/>
@@ -3956,41 +3970,41 @@
       <c r="B10" s="67"/>
       <c r="C10" s="52"/>
       <c r="D10" s="94" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E10" s="94" t="s">
-        <v>267</v>
+        <v>335</v>
       </c>
       <c r="F10" s="94"/>
       <c r="G10" s="94"/>
       <c r="H10" s="94" t="s">
-        <v>269</v>
+        <v>336</v>
       </c>
       <c r="I10" s="94" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="J10" s="94" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="K10" s="94"/>
       <c r="L10" s="94" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="M10" s="94" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="N10" s="94" t="s">
-        <v>277</v>
+        <v>323</v>
       </c>
       <c r="O10" s="94" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="P10" s="94"/>
       <c r="Q10" s="94" t="s">
-        <v>281</v>
+        <v>337</v>
       </c>
       <c r="R10" s="94" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="S10" s="58"/>
       <c r="V10" s="100"/>
@@ -4020,45 +4034,45 @@
       <c r="B12" s="65"/>
       <c r="C12" s="52"/>
       <c r="D12" s="89" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="E12" s="89" t="s">
-        <v>256</v>
+        <v>329</v>
       </c>
       <c r="F12" s="89"/>
       <c r="G12" s="89" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H12" s="89" t="s">
-        <v>276</v>
+        <v>322</v>
       </c>
       <c r="I12" s="89" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="J12" s="89" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="K12" s="89"/>
       <c r="L12" s="89" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="M12" s="89" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="N12" s="89" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="O12" s="89" t="s">
-        <v>256</v>
+        <v>329</v>
       </c>
       <c r="P12" s="89" t="s">
-        <v>292</v>
+        <v>342</v>
       </c>
       <c r="Q12" s="89" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="R12" s="89" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="S12" s="53"/>
       <c r="V12" s="100"/>
@@ -4078,7 +4092,7 @@
       <c r="F13" s="72" t="s">
         <v>168</v>
       </c>
-      <c r="G13" s="72" t="s">
+      <c r="G13" s="105" t="s">
         <v>213</v>
       </c>
       <c r="H13" s="72" t="s">
@@ -4099,7 +4113,7 @@
       <c r="M13" s="72" t="s">
         <v>221</v>
       </c>
-      <c r="N13" s="72" t="s">
+      <c r="N13" s="105" t="s">
         <v>222</v>
       </c>
       <c r="O13" s="72" t="s">
@@ -4121,45 +4135,45 @@
       <c r="B14" s="67"/>
       <c r="C14" s="52"/>
       <c r="D14" s="94" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="E14" s="94" t="s">
-        <v>257</v>
+        <v>330</v>
       </c>
       <c r="F14" s="94"/>
       <c r="G14" s="94" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H14" s="94" t="s">
-        <v>277</v>
+        <v>323</v>
       </c>
       <c r="I14" s="94" t="s">
-        <v>285</v>
+        <v>338</v>
       </c>
       <c r="J14" s="94" t="s">
-        <v>287</v>
+        <v>339</v>
       </c>
       <c r="K14" s="94"/>
       <c r="L14" s="94" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="M14" s="94" t="s">
-        <v>289</v>
+        <v>340</v>
       </c>
       <c r="N14" s="94" t="s">
-        <v>291</v>
+        <v>341</v>
       </c>
       <c r="O14" s="94" t="s">
-        <v>257</v>
+        <v>330</v>
       </c>
       <c r="P14" s="94" t="s">
-        <v>293</v>
+        <v>343</v>
       </c>
       <c r="Q14" s="94" t="s">
-        <v>285</v>
+        <v>338</v>
       </c>
       <c r="R14" s="94" t="s">
-        <v>287</v>
+        <v>339</v>
       </c>
       <c r="S14" s="58"/>
       <c r="V14" s="69"/>
@@ -4190,35 +4204,35 @@
       <c r="C16" s="52"/>
       <c r="D16" s="89"/>
       <c r="E16" s="89" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="F16" s="89" t="s">
-        <v>256</v>
+        <v>329</v>
       </c>
       <c r="G16" s="89" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="H16" s="89"/>
       <c r="I16" s="89" t="s">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="J16" s="89"/>
       <c r="K16" s="89" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="L16" s="89"/>
       <c r="M16" s="89" t="s">
-        <v>300</v>
+        <v>279</v>
       </c>
       <c r="N16" s="89"/>
       <c r="O16" s="89" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="P16" s="89" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="Q16" s="89" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="R16" s="89"/>
       <c r="S16" s="53"/>
@@ -4233,7 +4247,7 @@
       <c r="D17" s="72" t="s">
         <v>168</v>
       </c>
-      <c r="E17" s="72" t="s">
+      <c r="E17" s="105" t="s">
         <v>222</v>
       </c>
       <c r="F17" s="72" t="s">
@@ -4245,7 +4259,7 @@
       <c r="H17" s="72" t="s">
         <v>195</v>
       </c>
-      <c r="I17" s="72" t="s">
+      <c r="I17" s="105" t="s">
         <v>224</v>
       </c>
       <c r="J17" s="72" t="s">
@@ -4257,7 +4271,7 @@
       <c r="L17" s="72" t="s">
         <v>195</v>
       </c>
-      <c r="M17" s="72" t="s">
+      <c r="M17" s="105" t="s">
         <v>226</v>
       </c>
       <c r="N17" s="72" t="s">
@@ -4283,35 +4297,35 @@
       <c r="C18" s="52"/>
       <c r="D18" s="94"/>
       <c r="E18" s="94" t="s">
-        <v>291</v>
+        <v>341</v>
       </c>
       <c r="F18" s="94" t="s">
-        <v>257</v>
+        <v>330</v>
       </c>
       <c r="G18" s="94" t="s">
-        <v>295</v>
+        <v>344</v>
       </c>
       <c r="H18" s="94"/>
       <c r="I18" s="94" t="s">
-        <v>297</v>
+        <v>345</v>
       </c>
       <c r="J18" s="94"/>
       <c r="K18" s="94" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="L18" s="94"/>
       <c r="M18" s="94" t="s">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="N18" s="94"/>
       <c r="O18" s="94" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="P18" s="94" t="s">
-        <v>285</v>
+        <v>338</v>
       </c>
       <c r="Q18" s="94" t="s">
-        <v>287</v>
+        <v>339</v>
       </c>
       <c r="R18" s="94"/>
       <c r="S18" s="58"/>
@@ -4342,45 +4356,45 @@
       <c r="B20" s="65"/>
       <c r="C20" s="52"/>
       <c r="D20" s="89" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="E20" s="89" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="F20" s="89" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="G20" s="89"/>
       <c r="H20" s="89" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="I20" s="89" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="J20" s="89" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="K20" s="89" t="s">
-        <v>302</v>
+        <v>281</v>
       </c>
       <c r="L20" s="89" t="s">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="M20" s="89" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="N20" s="89" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="O20" s="89"/>
       <c r="P20" s="89" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="Q20" s="89" t="s">
-        <v>256</v>
+        <v>329</v>
       </c>
       <c r="R20" s="89" t="s">
-        <v>276</v>
+        <v>322</v>
       </c>
       <c r="S20" s="53"/>
       <c r="V20" s="69"/>
@@ -4427,7 +4441,7 @@
       <c r="O21" s="72" t="s">
         <v>168</v>
       </c>
-      <c r="P21" s="72" t="s">
+      <c r="P21" s="105" t="s">
         <v>222</v>
       </c>
       <c r="Q21" s="72" t="s">
@@ -4443,45 +4457,45 @@
       <c r="B22" s="67"/>
       <c r="C22" s="52"/>
       <c r="D22" s="94" t="s">
-        <v>269</v>
+        <v>336</v>
       </c>
       <c r="E22" s="94" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="F22" s="94" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="G22" s="94"/>
       <c r="H22" s="94" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="I22" s="94" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="J22" s="94" t="s">
-        <v>281</v>
+        <v>337</v>
       </c>
       <c r="K22" s="94" t="s">
-        <v>303</v>
+        <v>282</v>
       </c>
       <c r="L22" s="94" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="M22" s="94" t="s">
-        <v>285</v>
+        <v>338</v>
       </c>
       <c r="N22" s="94" t="s">
-        <v>287</v>
+        <v>339</v>
       </c>
       <c r="O22" s="94"/>
       <c r="P22" s="94" t="s">
-        <v>291</v>
+        <v>341</v>
       </c>
       <c r="Q22" s="94" t="s">
-        <v>257</v>
+        <v>330</v>
       </c>
       <c r="R22" s="94" t="s">
-        <v>277</v>
+        <v>323</v>
       </c>
       <c r="S22" s="58"/>
       <c r="V22" s="69"/>
@@ -4511,42 +4525,42 @@
       <c r="B24" s="65"/>
       <c r="C24" s="52"/>
       <c r="D24" s="89" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="E24" s="89"/>
       <c r="F24" s="89" t="s">
-        <v>308</v>
+        <v>348</v>
       </c>
       <c r="G24" s="89" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="H24" s="89" t="s">
-        <v>312</v>
+        <v>287</v>
       </c>
       <c r="I24" s="89"/>
       <c r="J24" s="89" t="s">
-        <v>314</v>
+        <v>288</v>
       </c>
       <c r="K24" s="89" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="L24" s="89" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="M24" s="89" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="N24" s="89" t="s">
-        <v>256</v>
+        <v>329</v>
       </c>
       <c r="O24" s="89" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="P24" s="89" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="Q24" s="89" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="R24" s="89"/>
       <c r="S24" s="53"/>
@@ -4585,7 +4599,7 @@
       <c r="L25" s="72" t="s">
         <v>194</v>
       </c>
-      <c r="M25" s="72" t="s">
+      <c r="M25" s="105" t="s">
         <v>222</v>
       </c>
       <c r="N25" s="72" t="s">
@@ -4610,48 +4624,48 @@
       <c r="B26" s="67"/>
       <c r="C26" s="52"/>
       <c r="D26" s="94" t="s">
-        <v>307</v>
+        <v>347</v>
       </c>
       <c r="E26" s="94"/>
       <c r="F26" s="94" t="s">
-        <v>309</v>
+        <v>349</v>
       </c>
       <c r="G26" s="94" t="s">
-        <v>311</v>
+        <v>286</v>
       </c>
       <c r="H26" s="94" t="s">
-        <v>313</v>
+        <v>350</v>
       </c>
       <c r="I26" s="94"/>
       <c r="J26" s="94" t="s">
-        <v>315</v>
+        <v>289</v>
       </c>
       <c r="K26" s="94" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="L26" s="94" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="M26" s="94" t="s">
-        <v>291</v>
+        <v>341</v>
       </c>
       <c r="N26" s="94" t="s">
-        <v>257</v>
+        <v>330</v>
       </c>
       <c r="O26" s="94" t="s">
-        <v>307</v>
+        <v>347</v>
       </c>
       <c r="P26" s="94" t="s">
-        <v>285</v>
+        <v>338</v>
       </c>
       <c r="Q26" s="94" t="s">
-        <v>287</v>
+        <v>339</v>
       </c>
       <c r="R26" s="94"/>
       <c r="S26" s="58"/>
       <c r="U26" s="1" t="str">
         <f xml:space="preserve"> MID($N$22,3,1)</f>
-        <v>˙</v>
+        <v>ˉ</v>
       </c>
       <c r="V26" s="69"/>
     </row>
@@ -4684,45 +4698,45 @@
       <c r="B28" s="65"/>
       <c r="C28" s="52"/>
       <c r="D28" s="89" t="s">
-        <v>316</v>
+        <v>290</v>
       </c>
       <c r="E28" s="89" t="s">
-        <v>318</v>
+        <v>292</v>
       </c>
       <c r="F28" s="89" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="G28" s="89" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="H28" s="89" t="s">
-        <v>322</v>
+        <v>294</v>
       </c>
       <c r="I28" s="89" t="s">
-        <v>324</v>
+        <v>296</v>
       </c>
       <c r="J28" s="89" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="K28" s="89"/>
       <c r="L28" s="89" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="M28" s="89" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="N28" s="89" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="O28" s="89"/>
       <c r="P28" s="89" t="s">
-        <v>276</v>
+        <v>322</v>
       </c>
       <c r="Q28" s="89" t="s">
-        <v>327</v>
+        <v>299</v>
       </c>
       <c r="R28" s="89" t="s">
-        <v>329</v>
+        <v>300</v>
       </c>
       <c r="S28" s="53"/>
       <c r="U28" s="1" t="e">
@@ -4746,16 +4760,16 @@
       <c r="F29" s="72" t="s">
         <v>228</v>
       </c>
-      <c r="G29" s="72" t="s">
+      <c r="G29" s="105" t="s">
         <v>222</v>
       </c>
       <c r="H29" s="72" t="s">
         <v>229</v>
       </c>
-      <c r="I29" s="72" t="s">
+      <c r="I29" s="105" t="s">
         <v>230</v>
       </c>
-      <c r="J29" s="72" t="s">
+      <c r="J29" s="105" t="s">
         <v>207</v>
       </c>
       <c r="K29" s="72" t="s">
@@ -4793,45 +4807,45 @@
       <c r="B30" s="67"/>
       <c r="C30" s="52"/>
       <c r="D30" s="94" t="s">
-        <v>317</v>
+        <v>291</v>
       </c>
       <c r="E30" s="94" t="s">
-        <v>319</v>
+        <v>293</v>
       </c>
       <c r="F30" s="94" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="G30" s="94" t="s">
-        <v>291</v>
+        <v>341</v>
       </c>
       <c r="H30" s="94" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="I30" s="94" t="s">
-        <v>295</v>
+        <v>351</v>
       </c>
       <c r="J30" s="94" t="s">
-        <v>326</v>
+        <v>298</v>
       </c>
       <c r="K30" s="94"/>
       <c r="L30" s="94" t="s">
-        <v>269</v>
+        <v>336</v>
       </c>
       <c r="M30" s="94" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="N30" s="94" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="O30" s="94"/>
       <c r="P30" s="94" t="s">
-        <v>277</v>
+        <v>323</v>
       </c>
       <c r="Q30" s="94" t="s">
-        <v>328</v>
+        <v>352</v>
       </c>
       <c r="R30" s="94" t="s">
-        <v>330</v>
+        <v>301</v>
       </c>
       <c r="S30" s="58"/>
       <c r="U30" s="1" t="s">
@@ -4864,41 +4878,41 @@
       <c r="B32" s="65"/>
       <c r="C32" s="52"/>
       <c r="D32" s="89" t="s">
-        <v>308</v>
+        <v>348</v>
       </c>
       <c r="E32" s="89"/>
       <c r="F32" s="89" t="s">
-        <v>331</v>
+        <v>302</v>
       </c>
       <c r="G32" s="89" t="s">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="H32" s="89" t="s">
-        <v>335</v>
+        <v>304</v>
       </c>
       <c r="I32" s="89" t="s">
-        <v>337</v>
+        <v>305</v>
       </c>
       <c r="J32" s="89" t="s">
-        <v>322</v>
+        <v>294</v>
       </c>
       <c r="K32" s="89" t="s">
-        <v>324</v>
+        <v>296</v>
       </c>
       <c r="L32" s="89" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="M32" s="89" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="N32" s="89"/>
       <c r="O32" s="89"/>
       <c r="P32" s="89"/>
       <c r="Q32" s="89" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="R32" s="89" t="s">
-        <v>339</v>
+        <v>306</v>
       </c>
       <c r="S32" s="53"/>
       <c r="V32" s="69"/>
@@ -4936,7 +4950,7 @@
       <c r="L33" s="72" t="s">
         <v>207</v>
       </c>
-      <c r="M33" s="72" t="s">
+      <c r="M33" s="105" t="s">
         <v>222</v>
       </c>
       <c r="N33" s="72" t="s">
@@ -4961,41 +4975,41 @@
       <c r="B34" s="67"/>
       <c r="C34" s="52"/>
       <c r="D34" s="94" t="s">
-        <v>309</v>
+        <v>349</v>
       </c>
       <c r="E34" s="94"/>
       <c r="F34" s="94" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="G34" s="94" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="H34" s="94" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="I34" s="94" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="J34" s="94" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="K34" s="94" t="s">
-        <v>295</v>
+        <v>351</v>
       </c>
       <c r="L34" s="94" t="s">
-        <v>326</v>
+        <v>298</v>
       </c>
       <c r="M34" s="94" t="s">
-        <v>291</v>
+        <v>341</v>
       </c>
       <c r="N34" s="94"/>
       <c r="O34" s="94"/>
       <c r="P34" s="94"/>
       <c r="Q34" s="94" t="s">
-        <v>291</v>
+        <v>341</v>
       </c>
       <c r="R34" s="94" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="S34" s="58"/>
       <c r="V34" s="69"/>
@@ -5026,34 +5040,34 @@
       <c r="C36" s="52"/>
       <c r="D36" s="89"/>
       <c r="E36" s="89" t="s">
-        <v>341</v>
+        <v>307</v>
       </c>
       <c r="F36" s="89" t="s">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="G36" s="89"/>
       <c r="H36" s="89"/>
       <c r="I36" s="89"/>
       <c r="J36" s="89" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="K36" s="89" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="L36" s="89" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="M36" s="89"/>
       <c r="N36" s="89" t="s">
-        <v>345</v>
+        <v>308</v>
       </c>
       <c r="O36" s="89"/>
       <c r="P36" s="89" t="s">
-        <v>347</v>
+        <v>310</v>
       </c>
       <c r="Q36" s="89"/>
       <c r="R36" s="89" t="s">
-        <v>349</v>
+        <v>311</v>
       </c>
       <c r="S36" s="53"/>
       <c r="V36" s="69"/>
@@ -5117,34 +5131,34 @@
       <c r="C38" s="52"/>
       <c r="D38" s="94"/>
       <c r="E38" s="94" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="F38" s="94" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="G38" s="94"/>
       <c r="H38" s="94"/>
       <c r="I38" s="94"/>
       <c r="J38" s="94" t="s">
-        <v>269</v>
+        <v>336</v>
       </c>
       <c r="K38" s="94" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="L38" s="94" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="M38" s="94"/>
       <c r="N38" s="94" t="s">
-        <v>346</v>
+        <v>309</v>
       </c>
       <c r="O38" s="94"/>
       <c r="P38" s="94" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="Q38" s="94"/>
       <c r="R38" s="94" t="s">
-        <v>350</v>
+        <v>312</v>
       </c>
       <c r="S38" s="58"/>
       <c r="V38" s="69"/>
@@ -5174,41 +5188,41 @@
       <c r="B40" s="65"/>
       <c r="C40" s="52"/>
       <c r="D40" s="89" t="s">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="E40" s="89"/>
       <c r="F40" s="89" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="G40" s="89" t="s">
-        <v>351</v>
+        <v>313</v>
       </c>
       <c r="H40" s="89"/>
       <c r="I40" s="89" t="s">
-        <v>353</v>
+        <v>315</v>
       </c>
       <c r="J40" s="89"/>
       <c r="K40" s="89" t="s">
-        <v>355</v>
+        <v>316</v>
       </c>
       <c r="L40" s="89" t="s">
-        <v>335</v>
+        <v>304</v>
       </c>
       <c r="M40" s="89" t="s">
-        <v>337</v>
+        <v>305</v>
       </c>
       <c r="N40" s="89"/>
       <c r="O40" s="89" t="s">
-        <v>322</v>
+        <v>294</v>
       </c>
       <c r="P40" s="89" t="s">
-        <v>324</v>
+        <v>296</v>
       </c>
       <c r="Q40" s="89" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="R40" s="89" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="S40" s="53"/>
       <c r="V40" s="69"/>
@@ -5240,7 +5254,7 @@
       <c r="J41" s="72" t="s">
         <v>195</v>
       </c>
-      <c r="K41" s="72" t="s">
+      <c r="K41" s="105" t="s">
         <v>241</v>
       </c>
       <c r="L41" s="72" t="s">
@@ -5255,7 +5269,7 @@
       <c r="O41" s="72" t="s">
         <v>229</v>
       </c>
-      <c r="P41" s="72" t="s">
+      <c r="P41" s="105" t="s">
         <v>230</v>
       </c>
       <c r="Q41" s="72" t="s">
@@ -5271,41 +5285,41 @@
       <c r="B42" s="67"/>
       <c r="C42" s="52"/>
       <c r="D42" s="94" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="E42" s="94"/>
       <c r="F42" s="94" t="s">
-        <v>263</v>
+        <v>333</v>
       </c>
       <c r="G42" s="94" t="s">
-        <v>352</v>
+        <v>314</v>
       </c>
       <c r="H42" s="94"/>
       <c r="I42" s="94" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="J42" s="94"/>
       <c r="K42" s="94" t="s">
+        <v>362</v>
+      </c>
+      <c r="L42" s="94" t="s">
+        <v>355</v>
+      </c>
+      <c r="M42" s="94" t="s">
         <v>356</v>
-      </c>
-      <c r="L42" s="94" t="s">
-        <v>336</v>
-      </c>
-      <c r="M42" s="94" t="s">
-        <v>338</v>
       </c>
       <c r="N42" s="94"/>
       <c r="O42" s="94" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="P42" s="94" t="s">
-        <v>295</v>
+        <v>351</v>
       </c>
       <c r="Q42" s="94" t="s">
-        <v>326</v>
+        <v>298</v>
       </c>
       <c r="R42" s="94" t="s">
-        <v>291</v>
+        <v>341</v>
       </c>
       <c r="S42" s="58"/>
       <c r="V42" s="69"/>
@@ -5338,29 +5352,29 @@
       <c r="E44" s="89"/>
       <c r="F44" s="89"/>
       <c r="G44" s="89" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="H44" s="89" t="s">
-        <v>339</v>
+        <v>306</v>
       </c>
       <c r="I44" s="89"/>
       <c r="J44" s="89" t="s">
-        <v>341</v>
+        <v>307</v>
       </c>
       <c r="K44" s="89" t="s">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="L44" s="89"/>
       <c r="M44" s="89"/>
       <c r="N44" s="89"/>
       <c r="O44" s="89" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="P44" s="89" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="Q44" s="89" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="R44" s="89"/>
       <c r="S44" s="53"/>
@@ -5427,29 +5441,29 @@
       <c r="E46" s="94"/>
       <c r="F46" s="94"/>
       <c r="G46" s="94" t="s">
-        <v>291</v>
+        <v>341</v>
       </c>
       <c r="H46" s="94" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="I46" s="94"/>
       <c r="J46" s="94" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="K46" s="94" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="L46" s="94"/>
       <c r="M46" s="94"/>
       <c r="N46" s="94"/>
       <c r="O46" s="94" t="s">
-        <v>269</v>
+        <v>336</v>
       </c>
       <c r="P46" s="94" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="Q46" s="94" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="R46" s="94"/>
       <c r="S46" s="58"/>
@@ -5480,47 +5494,47 @@
       <c r="B48" s="65"/>
       <c r="C48" s="52"/>
       <c r="D48" s="89" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="E48" s="89" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="F48" s="89" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G48" s="89" t="s">
-        <v>256</v>
+        <v>329</v>
       </c>
       <c r="H48" s="89" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="I48" s="89" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="J48" s="89" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="K48" s="89"/>
       <c r="L48" s="89" t="s">
-        <v>318</v>
+        <v>292</v>
       </c>
       <c r="M48" s="89" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="N48" s="89" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="O48" s="89" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="P48" s="89" t="s">
-        <v>302</v>
+        <v>281</v>
       </c>
       <c r="Q48" s="89" t="s">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="R48" s="89" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="S48" s="53"/>
       <c r="V48" s="69"/>
@@ -5583,47 +5597,47 @@
       <c r="B50" s="67"/>
       <c r="C50" s="52"/>
       <c r="D50" s="94" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="E50" s="94" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="F50" s="94" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G50" s="94" t="s">
-        <v>257</v>
+        <v>330</v>
       </c>
       <c r="H50" s="94" t="s">
-        <v>307</v>
+        <v>347</v>
       </c>
       <c r="I50" s="94" t="s">
-        <v>285</v>
+        <v>338</v>
       </c>
       <c r="J50" s="94" t="s">
-        <v>287</v>
+        <v>339</v>
       </c>
       <c r="K50" s="94"/>
       <c r="L50" s="94" t="s">
-        <v>319</v>
+        <v>293</v>
       </c>
       <c r="M50" s="94" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="N50" s="94" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="O50" s="94" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="P50" s="94" t="s">
-        <v>303</v>
+        <v>282</v>
       </c>
       <c r="Q50" s="94" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="R50" s="94" t="s">
-        <v>291</v>
+        <v>341</v>
       </c>
       <c r="S50" s="58"/>
       <c r="V50" s="69"/>
@@ -5653,45 +5667,45 @@
       <c r="B52" s="65"/>
       <c r="C52" s="52"/>
       <c r="D52" s="89" t="s">
-        <v>322</v>
+        <v>294</v>
       </c>
       <c r="E52" s="89" t="s">
-        <v>324</v>
+        <v>296</v>
       </c>
       <c r="F52" s="89" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="G52" s="89"/>
       <c r="H52" s="89" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="I52" s="89" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="J52" s="89" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="K52" s="89"/>
       <c r="L52" s="89" t="s">
+        <v>261</v>
+      </c>
+      <c r="M52" s="89" t="s">
+        <v>265</v>
+      </c>
+      <c r="N52" s="89" t="s">
+        <v>319</v>
+      </c>
+      <c r="O52" s="89" t="s">
+        <v>269</v>
+      </c>
+      <c r="P52" s="89" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q52" s="89" t="s">
         <v>270</v>
       </c>
-      <c r="M52" s="89" t="s">
-        <v>274</v>
-      </c>
-      <c r="N52" s="89" t="s">
-        <v>359</v>
-      </c>
-      <c r="O52" s="89" t="s">
-        <v>280</v>
-      </c>
-      <c r="P52" s="89" t="s">
-        <v>302</v>
-      </c>
-      <c r="Q52" s="89" t="s">
-        <v>282</v>
-      </c>
       <c r="R52" s="89" t="s">
-        <v>361</v>
+        <v>321</v>
       </c>
       <c r="S52" s="53"/>
       <c r="V52" s="69"/>
@@ -5754,45 +5768,45 @@
       <c r="B54" s="67"/>
       <c r="C54" s="52"/>
       <c r="D54" s="94" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="E54" s="94" t="s">
-        <v>295</v>
+        <v>351</v>
       </c>
       <c r="F54" s="94" t="s">
-        <v>326</v>
+        <v>298</v>
       </c>
       <c r="G54" s="94"/>
       <c r="H54" s="94" t="s">
-        <v>269</v>
+        <v>336</v>
       </c>
       <c r="I54" s="94" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="J54" s="94" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="K54" s="94"/>
       <c r="L54" s="94" t="s">
+        <v>262</v>
+      </c>
+      <c r="M54" s="94" t="s">
+        <v>266</v>
+      </c>
+      <c r="N54" s="94" t="s">
+        <v>320</v>
+      </c>
+      <c r="O54" s="94" t="s">
+        <v>337</v>
+      </c>
+      <c r="P54" s="94" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q54" s="94" t="s">
         <v>271</v>
       </c>
-      <c r="M54" s="94" t="s">
-        <v>275</v>
-      </c>
-      <c r="N54" s="94" t="s">
-        <v>360</v>
-      </c>
-      <c r="O54" s="94" t="s">
-        <v>281</v>
-      </c>
-      <c r="P54" s="94" t="s">
-        <v>303</v>
-      </c>
-      <c r="Q54" s="94" t="s">
-        <v>283</v>
-      </c>
       <c r="R54" s="94" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S54" s="58"/>
       <c r="V54" s="69"/>
@@ -5822,7 +5836,7 @@
       <c r="B56" s="65"/>
       <c r="C56" s="52"/>
       <c r="D56" s="89" t="s">
-        <v>256</v>
+        <v>329</v>
       </c>
       <c r="E56" s="89"/>
       <c r="F56" s="89"/>
@@ -5875,7 +5889,7 @@
       <c r="B58" s="67"/>
       <c r="C58" s="52"/>
       <c r="D58" s="94" t="s">
-        <v>257</v>
+        <v>330</v>
       </c>
       <c r="E58" s="94"/>
       <c r="F58" s="94"/>

--- a/output2/【河洛話注音】金剛般若波羅蜜經004。妙行無住分第四.xlsx
+++ b/output2/【河洛話注音】金剛般若波羅蜜經004。妙行無住分第四.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C84354-FA63-4153-B708-0E97BDD9B211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F4FDF6D-6DAD-4B86-BB16-749AFBA42DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28545" yWindow="405" windowWidth="27645" windowHeight="15585" activeTab="1" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
   </bookViews>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="368">
   <si>
     <t>【台羅拼音】</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1094,9 +1094,6 @@
     <t>，</t>
   </si>
   <si>
-    <t>若</t>
-  </si>
-  <si>
     <t>分</t>
   </si>
   <si>
@@ -1261,15 +1258,9 @@
     <t>聲</t>
   </si>
   <si>
-    <t>香</t>
-  </si>
-  <si>
     <t>味</t>
   </si>
   <si>
-    <t>觸</t>
-  </si>
-  <si>
     <t>福</t>
   </si>
   <si>
@@ -1300,19 +1291,10 @@
     <t>也</t>
   </si>
   <si>
-    <t>西</t>
-  </si>
-  <si>
-    <t>北</t>
-  </si>
-  <si>
     <t>維</t>
   </si>
   <si>
     <t>上</t>
-  </si>
-  <si>
-    <t>下</t>
   </si>
   <si>
     <t>亦</t>
@@ -1347,22 +1329,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hang5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄤˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bo5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆠㄜˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hun1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1371,10 +1337,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>si3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hok8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1443,30 +1405,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>m7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>siann1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>phang1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>bi7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>tak4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄚㆻ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ju5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1495,14 +1441,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>na2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄋㄚˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ki5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1527,18 +1465,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sur1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>liang5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㄧㄤˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>i3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1583,18 +1509,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sai1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pak4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄅㄚㆻ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>i5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1607,10 +1521,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>e7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>iah8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1675,10 +1585,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄒㄧ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>cu3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1707,10 +1613,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㆬ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>sik4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1723,10 +1625,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄆㄤˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ㆠㄧ˫</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1747,10 +1645,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄙˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ㄧ˪</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1783,19 +1677,147 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄙㄞˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ㄒㄧㄤ˫</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㆤ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ㄍㄚ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>思</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>四</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>香</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>觸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hing5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄧㄥˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>su3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄨ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>put4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄅㄨㆵ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hiong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄧㆲˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ciok4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄑㄧㆦㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>liong7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㄧㆲ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>無</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hiu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>北</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bu5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆠㄨˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jiok8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆢㄧㆦㆻ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄧㄨˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>se1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㆤˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pok4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄅㆦㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ha7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄚ˫</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2542,7 +2564,7 @@
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2831,6 +2853,12 @@
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="63" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
@@ -2847,9 +2875,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3589,15 +3614,15 @@
         <v>167</v>
       </c>
       <c r="C5" s="70" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="B6" s="95" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="C6" s="96" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" spans="2:3">
@@ -3610,7 +3635,7 @@
     </row>
     <row r="9" spans="2:3">
       <c r="B9" s="95" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C9" s="97">
         <v>40</v>
@@ -3618,7 +3643,7 @@
     </row>
     <row r="10" spans="2:3">
       <c r="B10" s="98" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C10" s="97">
         <v>15</v>
@@ -3738,32 +3763,32 @@
       <c r="R3" s="77"/>
       <c r="S3" s="74"/>
       <c r="T3" s="71"/>
-      <c r="V3" s="99" t="s">
-        <v>245</v>
+      <c r="V3" s="101" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B4" s="65"/>
       <c r="D4" s="89" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="E4" s="89" t="s">
-        <v>251</v>
+        <v>339</v>
       </c>
       <c r="F4" s="89" t="s">
-        <v>253</v>
+        <v>357</v>
       </c>
       <c r="G4" s="89" t="s">
-        <v>329</v>
+        <v>305</v>
       </c>
       <c r="H4" s="89" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="I4" s="89" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="J4" s="89" t="s">
-        <v>257</v>
+        <v>341</v>
       </c>
       <c r="K4" s="89"/>
       <c r="L4" s="89"/>
@@ -3774,32 +3799,32 @@
       <c r="Q4" s="89"/>
       <c r="R4" s="89"/>
       <c r="S4" s="53"/>
-      <c r="V4" s="100"/>
+      <c r="V4" s="102"/>
     </row>
     <row r="5" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B5" s="66">
         <v>1</v>
       </c>
       <c r="D5" s="72" t="s">
+        <v>211</v>
+      </c>
+      <c r="E5" s="99" t="s">
         <v>212</v>
       </c>
-      <c r="E5" s="105" t="s">
-        <v>213</v>
-      </c>
-      <c r="F5" s="72" t="s">
-        <v>206</v>
+      <c r="F5" s="100" t="s">
+        <v>351</v>
       </c>
       <c r="G5" s="72" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H5" s="72" t="s">
+        <v>169</v>
+      </c>
+      <c r="I5" s="72" t="s">
         <v>170</v>
       </c>
-      <c r="I5" s="72" t="s">
-        <v>171</v>
-      </c>
-      <c r="J5" s="72" t="s">
-        <v>214</v>
+      <c r="J5" s="99" t="s">
+        <v>335</v>
       </c>
       <c r="K5" s="72"/>
       <c r="L5" s="72"/>
@@ -3810,31 +3835,31 @@
       <c r="Q5" s="72"/>
       <c r="R5" s="72"/>
       <c r="S5" s="54"/>
-      <c r="V5" s="100"/>
+      <c r="V5" s="102"/>
     </row>
     <row r="6" spans="2:22" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="B6" s="67"/>
       <c r="C6" s="51"/>
       <c r="D6" s="94" t="s">
-        <v>328</v>
+        <v>304</v>
       </c>
       <c r="E6" s="94" t="s">
-        <v>252</v>
+        <v>340</v>
       </c>
       <c r="F6" s="94" t="s">
-        <v>254</v>
+        <v>358</v>
       </c>
       <c r="G6" s="94" t="s">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="H6" s="94" t="s">
-        <v>331</v>
+        <v>307</v>
       </c>
       <c r="I6" s="94" t="s">
-        <v>332</v>
+        <v>308</v>
       </c>
       <c r="J6" s="94" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="K6" s="94"/>
       <c r="L6" s="94"/>
@@ -3845,7 +3870,7 @@
       <c r="Q6" s="94"/>
       <c r="R6" s="94"/>
       <c r="S6" s="55"/>
-      <c r="V6" s="100"/>
+      <c r="V6" s="102"/>
     </row>
     <row r="7" spans="2:22" s="49" customFormat="1" ht="60" customHeight="1">
       <c r="B7" s="64"/>
@@ -3866,50 +3891,50 @@
       <c r="Q7" s="82"/>
       <c r="R7" s="82"/>
       <c r="S7" s="57"/>
-      <c r="V7" s="100"/>
+      <c r="V7" s="102"/>
     </row>
     <row r="8" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="65"/>
       <c r="C8" s="52"/>
       <c r="D8" s="89" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="E8" s="89" t="s">
-        <v>334</v>
+        <v>309</v>
       </c>
       <c r="F8" s="89"/>
       <c r="G8" s="89"/>
       <c r="H8" s="89" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="I8" s="89" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="J8" s="89" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="K8" s="89"/>
       <c r="L8" s="89" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="M8" s="89" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="N8" s="89" t="s">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="O8" s="89" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="P8" s="89"/>
       <c r="Q8" s="89" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="R8" s="89" t="s">
-        <v>253</v>
+        <v>357</v>
       </c>
       <c r="S8" s="53"/>
-      <c r="V8" s="100"/>
+      <c r="V8" s="102"/>
     </row>
     <row r="9" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B9" s="66">
@@ -3918,96 +3943,96 @@
       </c>
       <c r="C9" s="52"/>
       <c r="D9" s="72" t="s">
+        <v>214</v>
+      </c>
+      <c r="E9" s="72" t="s">
         <v>215</v>
       </c>
-      <c r="E9" s="72" t="s">
+      <c r="F9" s="72" t="s">
+        <v>173</v>
+      </c>
+      <c r="G9" s="72" t="s">
+        <v>191</v>
+      </c>
+      <c r="H9" s="72" t="s">
+        <v>188</v>
+      </c>
+      <c r="I9" s="72" t="s">
+        <v>189</v>
+      </c>
+      <c r="J9" s="72" t="s">
+        <v>190</v>
+      </c>
+      <c r="K9" s="72" t="s">
+        <v>192</v>
+      </c>
+      <c r="L9" s="72" t="s">
+        <v>189</v>
+      </c>
+      <c r="M9" s="72" t="s">
+        <v>193</v>
+      </c>
+      <c r="N9" s="72" t="s">
         <v>216</v>
       </c>
-      <c r="F9" s="72" t="s">
-        <v>174</v>
-      </c>
-      <c r="G9" s="72" t="s">
-        <v>192</v>
-      </c>
-      <c r="H9" s="72" t="s">
-        <v>189</v>
-      </c>
-      <c r="I9" s="72" t="s">
-        <v>190</v>
-      </c>
-      <c r="J9" s="72" t="s">
-        <v>191</v>
-      </c>
-      <c r="K9" s="72" t="s">
-        <v>193</v>
-      </c>
-      <c r="L9" s="72" t="s">
-        <v>190</v>
-      </c>
-      <c r="M9" s="72" t="s">
-        <v>194</v>
-      </c>
-      <c r="N9" s="72" t="s">
+      <c r="O9" s="72" t="s">
         <v>217</v>
-      </c>
-      <c r="O9" s="72" t="s">
-        <v>218</v>
       </c>
       <c r="P9" s="72" t="s">
         <v>168</v>
       </c>
       <c r="Q9" s="72" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R9" s="72" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S9" s="54"/>
       <c r="T9" s="71"/>
-      <c r="V9" s="100"/>
+      <c r="V9" s="102"/>
     </row>
     <row r="10" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="67"/>
       <c r="C10" s="52"/>
       <c r="D10" s="94" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="E10" s="94" t="s">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="F10" s="94"/>
       <c r="G10" s="94"/>
       <c r="H10" s="94" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="I10" s="94" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="J10" s="94" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="K10" s="94"/>
       <c r="L10" s="94" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="M10" s="94" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="N10" s="94" t="s">
-        <v>323</v>
+        <v>299</v>
       </c>
       <c r="O10" s="94" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="P10" s="94"/>
       <c r="Q10" s="94" t="s">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="R10" s="94" t="s">
-        <v>254</v>
+        <v>358</v>
       </c>
       <c r="S10" s="58"/>
-      <c r="V10" s="100"/>
+      <c r="V10" s="102"/>
     </row>
     <row r="11" spans="2:22" s="83" customFormat="1" ht="60" customHeight="1">
       <c r="B11" s="80"/>
@@ -4028,54 +4053,54 @@
       <c r="Q11" s="79"/>
       <c r="R11" s="79"/>
       <c r="S11" s="57"/>
-      <c r="V11" s="100"/>
+      <c r="V11" s="102"/>
     </row>
     <row r="12" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="65"/>
       <c r="C12" s="52"/>
       <c r="D12" s="89" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="E12" s="89" t="s">
-        <v>329</v>
+        <v>305</v>
       </c>
       <c r="F12" s="89"/>
       <c r="G12" s="89" t="s">
-        <v>251</v>
+        <v>339</v>
       </c>
       <c r="H12" s="89" t="s">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="I12" s="89" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="J12" s="89" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="K12" s="89"/>
       <c r="L12" s="89" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="M12" s="89" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="N12" s="89" t="s">
-        <v>275</v>
+        <v>343</v>
       </c>
       <c r="O12" s="89" t="s">
-        <v>329</v>
+        <v>305</v>
       </c>
       <c r="P12" s="89" t="s">
-        <v>342</v>
+        <v>316</v>
       </c>
       <c r="Q12" s="89" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="R12" s="89" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="S12" s="53"/>
-      <c r="V12" s="100"/>
+      <c r="V12" s="102"/>
     </row>
     <row r="13" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B13" s="66">
@@ -4084,96 +4109,96 @@
       </c>
       <c r="C13" s="52"/>
       <c r="D13" s="72" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E13" s="72" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F13" s="72" t="s">
         <v>168</v>
       </c>
-      <c r="G13" s="105" t="s">
-        <v>213</v>
+      <c r="G13" s="99" t="s">
+        <v>212</v>
       </c>
       <c r="H13" s="72" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I13" s="72" t="s">
+        <v>218</v>
+      </c>
+      <c r="J13" s="72" t="s">
         <v>219</v>
       </c>
-      <c r="J13" s="72" t="s">
+      <c r="K13" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="L13" s="72" t="s">
+        <v>201</v>
+      </c>
+      <c r="M13" s="72" t="s">
         <v>220</v>
       </c>
-      <c r="K13" s="72" t="s">
-        <v>175</v>
-      </c>
-      <c r="L13" s="72" t="s">
-        <v>202</v>
-      </c>
-      <c r="M13" s="72" t="s">
+      <c r="N13" s="99" t="s">
         <v>221</v>
       </c>
-      <c r="N13" s="105" t="s">
-        <v>222</v>
-      </c>
       <c r="O13" s="72" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P13" s="72" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q13" s="72" t="s">
+        <v>218</v>
+      </c>
+      <c r="R13" s="72" t="s">
         <v>219</v>
       </c>
-      <c r="R13" s="72" t="s">
-        <v>220</v>
-      </c>
       <c r="S13" s="54"/>
-      <c r="V13" s="101"/>
+      <c r="V13" s="103"/>
     </row>
     <row r="14" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="67"/>
       <c r="C14" s="52"/>
       <c r="D14" s="94" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="E14" s="94" t="s">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="F14" s="94"/>
       <c r="G14" s="94" t="s">
-        <v>252</v>
+        <v>340</v>
       </c>
       <c r="H14" s="94" t="s">
-        <v>323</v>
+        <v>299</v>
       </c>
       <c r="I14" s="94" t="s">
-        <v>338</v>
+        <v>313</v>
       </c>
       <c r="J14" s="94" t="s">
-        <v>339</v>
+        <v>314</v>
       </c>
       <c r="K14" s="94"/>
       <c r="L14" s="94" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="M14" s="94" t="s">
-        <v>340</v>
+        <v>315</v>
       </c>
       <c r="N14" s="94" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="O14" s="94" t="s">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="P14" s="94" t="s">
-        <v>343</v>
+        <v>317</v>
       </c>
       <c r="Q14" s="94" t="s">
-        <v>338</v>
+        <v>313</v>
       </c>
       <c r="R14" s="94" t="s">
-        <v>339</v>
+        <v>314</v>
       </c>
       <c r="S14" s="58"/>
       <c r="V14" s="69"/>
@@ -4204,35 +4229,35 @@
       <c r="C16" s="52"/>
       <c r="D16" s="89"/>
       <c r="E16" s="89" t="s">
-        <v>275</v>
+        <v>343</v>
       </c>
       <c r="F16" s="89" t="s">
-        <v>329</v>
+        <v>305</v>
       </c>
       <c r="G16" s="89" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="H16" s="89"/>
       <c r="I16" s="89" t="s">
-        <v>277</v>
+        <v>345</v>
       </c>
       <c r="J16" s="89"/>
       <c r="K16" s="89" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="L16" s="89"/>
       <c r="M16" s="89" t="s">
-        <v>279</v>
+        <v>347</v>
       </c>
       <c r="N16" s="89"/>
       <c r="O16" s="89" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="P16" s="89" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="Q16" s="89" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="R16" s="89"/>
       <c r="S16" s="53"/>
@@ -4247,47 +4272,47 @@
       <c r="D17" s="72" t="s">
         <v>168</v>
       </c>
-      <c r="E17" s="105" t="s">
+      <c r="E17" s="99" t="s">
+        <v>221</v>
+      </c>
+      <c r="F17" s="72" t="s">
+        <v>198</v>
+      </c>
+      <c r="G17" s="72" t="s">
         <v>222</v>
       </c>
-      <c r="F17" s="72" t="s">
-        <v>199</v>
-      </c>
-      <c r="G17" s="72" t="s">
+      <c r="H17" s="72" t="s">
+        <v>194</v>
+      </c>
+      <c r="I17" s="99" t="s">
+        <v>336</v>
+      </c>
+      <c r="J17" s="72" t="s">
+        <v>194</v>
+      </c>
+      <c r="K17" s="72" t="s">
         <v>223</v>
       </c>
-      <c r="H17" s="72" t="s">
-        <v>195</v>
-      </c>
-      <c r="I17" s="105" t="s">
-        <v>224</v>
-      </c>
-      <c r="J17" s="72" t="s">
-        <v>195</v>
-      </c>
-      <c r="K17" s="72" t="s">
-        <v>225</v>
-      </c>
       <c r="L17" s="72" t="s">
-        <v>195</v>
-      </c>
-      <c r="M17" s="105" t="s">
-        <v>226</v>
+        <v>194</v>
+      </c>
+      <c r="M17" s="99" t="s">
+        <v>337</v>
       </c>
       <c r="N17" s="72" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O17" s="72" t="s">
+        <v>217</v>
+      </c>
+      <c r="P17" s="72" t="s">
         <v>218</v>
       </c>
-      <c r="P17" s="72" t="s">
+      <c r="Q17" s="72" t="s">
         <v>219</v>
       </c>
-      <c r="Q17" s="72" t="s">
-        <v>220</v>
-      </c>
       <c r="R17" s="72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="S17" s="54"/>
       <c r="V17" s="69"/>
@@ -4297,35 +4322,35 @@
       <c r="C18" s="52"/>
       <c r="D18" s="94"/>
       <c r="E18" s="94" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F18" s="94" t="s">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="G18" s="94" t="s">
-        <v>344</v>
+        <v>318</v>
       </c>
       <c r="H18" s="94"/>
       <c r="I18" s="94" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J18" s="94"/>
       <c r="K18" s="94" t="s">
-        <v>346</v>
+        <v>319</v>
       </c>
       <c r="L18" s="94"/>
       <c r="M18" s="94" t="s">
-        <v>280</v>
+        <v>348</v>
       </c>
       <c r="N18" s="94"/>
       <c r="O18" s="94" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="P18" s="94" t="s">
-        <v>338</v>
+        <v>313</v>
       </c>
       <c r="Q18" s="94" t="s">
-        <v>339</v>
+        <v>314</v>
       </c>
       <c r="R18" s="94"/>
       <c r="S18" s="58"/>
@@ -4356,45 +4381,45 @@
       <c r="B20" s="65"/>
       <c r="C20" s="52"/>
       <c r="D20" s="89" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="E20" s="89" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="F20" s="89" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="G20" s="89"/>
       <c r="H20" s="89" t="s">
+        <v>250</v>
+      </c>
+      <c r="I20" s="89" t="s">
+        <v>254</v>
+      </c>
+      <c r="J20" s="89" t="s">
+        <v>258</v>
+      </c>
+      <c r="K20" s="89" t="s">
+        <v>266</v>
+      </c>
+      <c r="L20" s="89" t="s">
+        <v>268</v>
+      </c>
+      <c r="M20" s="89" t="s">
         <v>261</v>
       </c>
-      <c r="I20" s="89" t="s">
-        <v>265</v>
-      </c>
-      <c r="J20" s="89" t="s">
-        <v>269</v>
-      </c>
-      <c r="K20" s="89" t="s">
-        <v>281</v>
-      </c>
-      <c r="L20" s="89" t="s">
-        <v>283</v>
-      </c>
-      <c r="M20" s="89" t="s">
-        <v>272</v>
-      </c>
       <c r="N20" s="89" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="O20" s="89"/>
       <c r="P20" s="89" t="s">
-        <v>275</v>
+        <v>343</v>
       </c>
       <c r="Q20" s="89" t="s">
-        <v>329</v>
+        <v>305</v>
       </c>
       <c r="R20" s="89" t="s">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="S20" s="53"/>
       <c r="V20" s="69"/>
@@ -4406,49 +4431,49 @@
       </c>
       <c r="C21" s="52"/>
       <c r="D21" s="72" t="s">
+        <v>188</v>
+      </c>
+      <c r="E21" s="72" t="s">
         <v>189</v>
       </c>
-      <c r="E21" s="72" t="s">
+      <c r="F21" s="72" t="s">
         <v>190</v>
       </c>
-      <c r="F21" s="72" t="s">
-        <v>191</v>
-      </c>
       <c r="G21" s="72" t="s">
+        <v>192</v>
+      </c>
+      <c r="H21" s="72" t="s">
+        <v>189</v>
+      </c>
+      <c r="I21" s="72" t="s">
         <v>193</v>
       </c>
-      <c r="H21" s="72" t="s">
-        <v>190</v>
-      </c>
-      <c r="I21" s="72" t="s">
-        <v>194</v>
-      </c>
       <c r="J21" s="72" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K21" s="72" t="s">
+        <v>171</v>
+      </c>
+      <c r="L21" s="72" t="s">
         <v>172</v>
       </c>
-      <c r="L21" s="72" t="s">
-        <v>173</v>
-      </c>
       <c r="M21" s="72" t="s">
+        <v>218</v>
+      </c>
+      <c r="N21" s="72" t="s">
         <v>219</v>
-      </c>
-      <c r="N21" s="72" t="s">
-        <v>220</v>
       </c>
       <c r="O21" s="72" t="s">
         <v>168</v>
       </c>
-      <c r="P21" s="105" t="s">
-        <v>222</v>
+      <c r="P21" s="99" t="s">
+        <v>221</v>
       </c>
       <c r="Q21" s="72" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="R21" s="72" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="S21" s="54"/>
       <c r="V21" s="69"/>
@@ -4457,45 +4482,45 @@
       <c r="B22" s="67"/>
       <c r="C22" s="52"/>
       <c r="D22" s="94" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="E22" s="94" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="F22" s="94" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="G22" s="94"/>
       <c r="H22" s="94" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="I22" s="94" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="J22" s="94" t="s">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="K22" s="94" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="L22" s="94" t="s">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="M22" s="94" t="s">
-        <v>338</v>
+        <v>313</v>
       </c>
       <c r="N22" s="94" t="s">
-        <v>339</v>
+        <v>314</v>
       </c>
       <c r="O22" s="94"/>
       <c r="P22" s="94" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q22" s="94" t="s">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="R22" s="94" t="s">
-        <v>323</v>
+        <v>299</v>
       </c>
       <c r="S22" s="58"/>
       <c r="V22" s="69"/>
@@ -4525,42 +4550,42 @@
       <c r="B24" s="65"/>
       <c r="C24" s="52"/>
       <c r="D24" s="89" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="E24" s="89"/>
       <c r="F24" s="89" t="s">
-        <v>348</v>
+        <v>321</v>
       </c>
       <c r="G24" s="89" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="H24" s="89" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="I24" s="89"/>
       <c r="J24" s="89" t="s">
-        <v>288</v>
+        <v>359</v>
       </c>
       <c r="K24" s="89" t="s">
+        <v>250</v>
+      </c>
+      <c r="L24" s="89" t="s">
+        <v>254</v>
+      </c>
+      <c r="M24" s="89" t="s">
+        <v>343</v>
+      </c>
+      <c r="N24" s="89" t="s">
+        <v>305</v>
+      </c>
+      <c r="O24" s="89" t="s">
+        <v>269</v>
+      </c>
+      <c r="P24" s="89" t="s">
         <v>261</v>
       </c>
-      <c r="L24" s="89" t="s">
-        <v>265</v>
-      </c>
-      <c r="M24" s="89" t="s">
-        <v>275</v>
-      </c>
-      <c r="N24" s="89" t="s">
-        <v>329</v>
-      </c>
-      <c r="O24" s="89" t="s">
-        <v>284</v>
-      </c>
-      <c r="P24" s="89" t="s">
-        <v>272</v>
-      </c>
       <c r="Q24" s="89" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="R24" s="89"/>
       <c r="S24" s="53"/>
@@ -4573,46 +4598,46 @@
       </c>
       <c r="C25" s="52"/>
       <c r="D25" s="72" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E25" s="72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F25" s="72" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G25" s="72" t="s">
+        <v>207</v>
+      </c>
+      <c r="H25" s="72" t="s">
         <v>208</v>
       </c>
-      <c r="H25" s="72" t="s">
+      <c r="I25" s="72" t="s">
+        <v>199</v>
+      </c>
+      <c r="J25" s="100" t="s">
+        <v>352</v>
+      </c>
+      <c r="K25" s="72" t="s">
+        <v>189</v>
+      </c>
+      <c r="L25" s="72" t="s">
+        <v>193</v>
+      </c>
+      <c r="M25" s="99" t="s">
+        <v>221</v>
+      </c>
+      <c r="N25" s="72" t="s">
+        <v>198</v>
+      </c>
+      <c r="O25" s="72" t="s">
         <v>209</v>
       </c>
-      <c r="I25" s="72" t="s">
-        <v>200</v>
-      </c>
-      <c r="J25" s="72" t="s">
-        <v>169</v>
-      </c>
-      <c r="K25" s="72" t="s">
-        <v>190</v>
-      </c>
-      <c r="L25" s="72" t="s">
-        <v>194</v>
-      </c>
-      <c r="M25" s="105" t="s">
-        <v>222</v>
-      </c>
-      <c r="N25" s="72" t="s">
-        <v>199</v>
-      </c>
-      <c r="O25" s="72" t="s">
-        <v>210</v>
-      </c>
       <c r="P25" s="72" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q25" s="72" t="s">
         <v>219</v>
-      </c>
-      <c r="Q25" s="72" t="s">
-        <v>220</v>
       </c>
       <c r="R25" s="72" t="s">
         <v>168</v>
@@ -4624,42 +4649,42 @@
       <c r="B26" s="67"/>
       <c r="C26" s="52"/>
       <c r="D26" s="94" t="s">
-        <v>347</v>
+        <v>320</v>
       </c>
       <c r="E26" s="94"/>
       <c r="F26" s="94" t="s">
-        <v>349</v>
+        <v>322</v>
       </c>
       <c r="G26" s="94" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="H26" s="94" t="s">
-        <v>350</v>
+        <v>323</v>
       </c>
       <c r="I26" s="94"/>
       <c r="J26" s="94" t="s">
-        <v>289</v>
+        <v>360</v>
       </c>
       <c r="K26" s="94" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="L26" s="94" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="M26" s="94" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="N26" s="94" t="s">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="O26" s="94" t="s">
-        <v>347</v>
+        <v>320</v>
       </c>
       <c r="P26" s="94" t="s">
-        <v>338</v>
+        <v>313</v>
       </c>
       <c r="Q26" s="94" t="s">
-        <v>339</v>
+        <v>314</v>
       </c>
       <c r="R26" s="94"/>
       <c r="S26" s="58"/>
@@ -4698,45 +4723,45 @@
       <c r="B28" s="65"/>
       <c r="C28" s="52"/>
       <c r="D28" s="89" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="E28" s="89" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="F28" s="89" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="G28" s="89" t="s">
-        <v>275</v>
+        <v>343</v>
       </c>
       <c r="H28" s="89" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="I28" s="89" t="s">
-        <v>296</v>
+        <v>249</v>
       </c>
       <c r="J28" s="89" t="s">
-        <v>297</v>
+        <v>349</v>
       </c>
       <c r="K28" s="89"/>
       <c r="L28" s="89" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="M28" s="89" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="N28" s="89" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="O28" s="89"/>
       <c r="P28" s="89" t="s">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="Q28" s="89" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="R28" s="89" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="S28" s="53"/>
       <c r="U28" s="1" t="e">
@@ -4752,49 +4777,49 @@
       </c>
       <c r="C29" s="52"/>
       <c r="D29" s="72" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E29" s="72" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F29" s="72" t="s">
+        <v>225</v>
+      </c>
+      <c r="G29" s="99" t="s">
+        <v>221</v>
+      </c>
+      <c r="H29" s="72" t="s">
+        <v>226</v>
+      </c>
+      <c r="I29" s="99" t="s">
+        <v>334</v>
+      </c>
+      <c r="J29" s="99" t="s">
+        <v>338</v>
+      </c>
+      <c r="K29" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="L29" s="72" t="s">
+        <v>188</v>
+      </c>
+      <c r="M29" s="72" t="s">
+        <v>189</v>
+      </c>
+      <c r="N29" s="72" t="s">
+        <v>190</v>
+      </c>
+      <c r="O29" s="72" t="s">
+        <v>192</v>
+      </c>
+      <c r="P29" s="72" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q29" s="72" t="s">
         <v>228</v>
       </c>
-      <c r="G29" s="105" t="s">
-        <v>222</v>
-      </c>
-      <c r="H29" s="72" t="s">
-        <v>229</v>
-      </c>
-      <c r="I29" s="105" t="s">
-        <v>230</v>
-      </c>
-      <c r="J29" s="105" t="s">
-        <v>207</v>
-      </c>
-      <c r="K29" s="72" t="s">
-        <v>175</v>
-      </c>
-      <c r="L29" s="72" t="s">
-        <v>189</v>
-      </c>
-      <c r="M29" s="72" t="s">
-        <v>190</v>
-      </c>
-      <c r="N29" s="72" t="s">
-        <v>191</v>
-      </c>
-      <c r="O29" s="72" t="s">
-        <v>193</v>
-      </c>
-      <c r="P29" s="72" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q29" s="72" t="s">
-        <v>231</v>
-      </c>
       <c r="R29" s="72" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="S29" s="54"/>
       <c r="U29" s="1" t="e">
@@ -4807,49 +4832,49 @@
       <c r="B30" s="67"/>
       <c r="C30" s="52"/>
       <c r="D30" s="94" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="E30" s="94" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="F30" s="94" t="s">
-        <v>326</v>
+        <v>302</v>
       </c>
       <c r="G30" s="94" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="H30" s="94" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="I30" s="94" t="s">
-        <v>351</v>
+        <v>311</v>
       </c>
       <c r="J30" s="94" t="s">
-        <v>298</v>
+        <v>350</v>
       </c>
       <c r="K30" s="94"/>
       <c r="L30" s="94" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="M30" s="94" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="N30" s="94" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="O30" s="94"/>
       <c r="P30" s="94" t="s">
-        <v>323</v>
+        <v>299</v>
       </c>
       <c r="Q30" s="94" t="s">
-        <v>352</v>
+        <v>324</v>
       </c>
       <c r="R30" s="94" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="S30" s="58"/>
       <c r="U30" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="V30" s="69"/>
     </row>
@@ -4865,7 +4890,9 @@
       <c r="J31" s="79"/>
       <c r="K31" s="79"/>
       <c r="L31" s="79"/>
-      <c r="M31" s="79"/>
+      <c r="M31" s="79" t="s">
+        <v>354</v>
+      </c>
       <c r="N31" s="79"/>
       <c r="O31" s="79"/>
       <c r="P31" s="79"/>
@@ -4878,41 +4905,41 @@
       <c r="B32" s="65"/>
       <c r="C32" s="52"/>
       <c r="D32" s="89" t="s">
-        <v>348</v>
+        <v>321</v>
       </c>
       <c r="E32" s="89"/>
       <c r="F32" s="89" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="G32" s="89" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="H32" s="89" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="I32" s="89" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="J32" s="89" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="K32" s="89" t="s">
-        <v>296</v>
+        <v>249</v>
       </c>
       <c r="L32" s="89" t="s">
-        <v>297</v>
+        <v>349</v>
       </c>
       <c r="M32" s="89" t="s">
-        <v>275</v>
+        <v>354</v>
       </c>
       <c r="N32" s="89"/>
       <c r="O32" s="89"/>
       <c r="P32" s="89"/>
       <c r="Q32" s="89" t="s">
-        <v>275</v>
+        <v>343</v>
       </c>
       <c r="R32" s="89" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="S32" s="53"/>
       <c r="V32" s="69"/>
@@ -4924,49 +4951,49 @@
       </c>
       <c r="C33" s="52"/>
       <c r="D33" s="72" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E33" s="72" t="s">
+        <v>199</v>
+      </c>
+      <c r="F33" s="72" t="s">
+        <v>229</v>
+      </c>
+      <c r="G33" s="72" t="s">
+        <v>230</v>
+      </c>
+      <c r="H33" s="72" t="s">
+        <v>231</v>
+      </c>
+      <c r="I33" s="72" t="s">
+        <v>232</v>
+      </c>
+      <c r="J33" s="72" t="s">
+        <v>226</v>
+      </c>
+      <c r="K33" s="72" t="s">
+        <v>227</v>
+      </c>
+      <c r="L33" s="72" t="s">
+        <v>206</v>
+      </c>
+      <c r="M33" s="99" t="s">
+        <v>221</v>
+      </c>
+      <c r="N33" s="72" t="s">
+        <v>199</v>
+      </c>
+      <c r="O33" s="72" t="s">
         <v>200</v>
       </c>
-      <c r="F33" s="72" t="s">
-        <v>232</v>
-      </c>
-      <c r="G33" s="72" t="s">
+      <c r="P33" s="72" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q33" s="72" t="s">
+        <v>221</v>
+      </c>
+      <c r="R33" s="72" t="s">
         <v>233</v>
-      </c>
-      <c r="H33" s="72" t="s">
-        <v>234</v>
-      </c>
-      <c r="I33" s="72" t="s">
-        <v>235</v>
-      </c>
-      <c r="J33" s="72" t="s">
-        <v>229</v>
-      </c>
-      <c r="K33" s="72" t="s">
-        <v>230</v>
-      </c>
-      <c r="L33" s="72" t="s">
-        <v>207</v>
-      </c>
-      <c r="M33" s="105" t="s">
-        <v>222</v>
-      </c>
-      <c r="N33" s="72" t="s">
-        <v>200</v>
-      </c>
-      <c r="O33" s="72" t="s">
-        <v>201</v>
-      </c>
-      <c r="P33" s="72" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q33" s="72" t="s">
-        <v>222</v>
-      </c>
-      <c r="R33" s="72" t="s">
-        <v>236</v>
       </c>
       <c r="S33" s="54"/>
       <c r="V33" s="69"/>
@@ -4975,41 +5002,41 @@
       <c r="B34" s="67"/>
       <c r="C34" s="52"/>
       <c r="D34" s="94" t="s">
-        <v>349</v>
+        <v>322</v>
       </c>
       <c r="E34" s="94"/>
       <c r="F34" s="94" t="s">
-        <v>353</v>
+        <v>325</v>
       </c>
       <c r="G34" s="94" t="s">
-        <v>354</v>
+        <v>326</v>
       </c>
       <c r="H34" s="94" t="s">
-        <v>355</v>
+        <v>327</v>
       </c>
       <c r="I34" s="94" t="s">
-        <v>356</v>
+        <v>328</v>
       </c>
       <c r="J34" s="94" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="K34" s="94" t="s">
-        <v>351</v>
+        <v>311</v>
       </c>
       <c r="L34" s="94" t="s">
-        <v>298</v>
+        <v>350</v>
       </c>
       <c r="M34" s="94" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="N34" s="94"/>
       <c r="O34" s="94"/>
       <c r="P34" s="94"/>
       <c r="Q34" s="94" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="R34" s="94" t="s">
-        <v>357</v>
+        <v>329</v>
       </c>
       <c r="S34" s="58"/>
       <c r="V34" s="69"/>
@@ -5040,34 +5067,34 @@
       <c r="C36" s="52"/>
       <c r="D36" s="89"/>
       <c r="E36" s="89" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="F36" s="89" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="G36" s="89"/>
       <c r="H36" s="89"/>
       <c r="I36" s="89"/>
       <c r="J36" s="89" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="K36" s="89" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="L36" s="89" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="M36" s="89"/>
       <c r="N36" s="89" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="O36" s="89"/>
       <c r="P36" s="89" t="s">
-        <v>310</v>
+        <v>362</v>
       </c>
       <c r="Q36" s="89"/>
       <c r="R36" s="89" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="S36" s="53"/>
       <c r="V36" s="69"/>
@@ -5082,46 +5109,46 @@
         <v>168</v>
       </c>
       <c r="E37" s="72" t="s">
+        <v>175</v>
+      </c>
+      <c r="F37" s="72" t="s">
         <v>176</v>
       </c>
-      <c r="F37" s="72" t="s">
-        <v>177</v>
-      </c>
       <c r="G37" s="72" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H37" s="72" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I37" s="72" t="s">
+        <v>191</v>
+      </c>
+      <c r="J37" s="72" t="s">
+        <v>188</v>
+      </c>
+      <c r="K37" s="72" t="s">
+        <v>189</v>
+      </c>
+      <c r="L37" s="72" t="s">
+        <v>190</v>
+      </c>
+      <c r="M37" s="72" t="s">
         <v>192</v>
       </c>
-      <c r="J37" s="72" t="s">
-        <v>189</v>
-      </c>
-      <c r="K37" s="72" t="s">
-        <v>190</v>
-      </c>
-      <c r="L37" s="72" t="s">
-        <v>191</v>
-      </c>
-      <c r="M37" s="72" t="s">
-        <v>193</v>
-      </c>
       <c r="N37" s="72" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O37" s="72" t="s">
-        <v>195</v>
-      </c>
-      <c r="P37" s="72" t="s">
-        <v>237</v>
+        <v>194</v>
+      </c>
+      <c r="P37" s="99" t="s">
+        <v>355</v>
       </c>
       <c r="Q37" s="72" t="s">
-        <v>195</v>
-      </c>
-      <c r="R37" s="72" t="s">
-        <v>238</v>
+        <v>194</v>
+      </c>
+      <c r="R37" s="99" t="s">
+        <v>356</v>
       </c>
       <c r="S37" s="54"/>
       <c r="V37" s="69"/>
@@ -5131,34 +5158,34 @@
       <c r="C38" s="52"/>
       <c r="D38" s="94"/>
       <c r="E38" s="94" t="s">
-        <v>358</v>
+        <v>330</v>
       </c>
       <c r="F38" s="94" t="s">
-        <v>359</v>
+        <v>331</v>
       </c>
       <c r="G38" s="94"/>
       <c r="H38" s="94"/>
       <c r="I38" s="94"/>
       <c r="J38" s="94" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="K38" s="94" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="L38" s="94" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="M38" s="94"/>
       <c r="N38" s="94" t="s">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="O38" s="94"/>
       <c r="P38" s="94" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q38" s="94"/>
       <c r="R38" s="94" t="s">
-        <v>312</v>
+        <v>365</v>
       </c>
       <c r="S38" s="58"/>
       <c r="V38" s="69"/>
@@ -5180,7 +5207,9 @@
       <c r="O39" s="79"/>
       <c r="P39" s="79"/>
       <c r="Q39" s="79"/>
-      <c r="R39" s="79"/>
+      <c r="R39" s="79" t="s">
+        <v>354</v>
+      </c>
       <c r="S39" s="85"/>
       <c r="V39" s="87"/>
     </row>
@@ -5188,41 +5217,41 @@
       <c r="B40" s="65"/>
       <c r="C40" s="52"/>
       <c r="D40" s="89" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="E40" s="89"/>
       <c r="F40" s="89" t="s">
-        <v>257</v>
+        <v>341</v>
       </c>
       <c r="G40" s="89" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="H40" s="89"/>
       <c r="I40" s="89" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="J40" s="89"/>
       <c r="K40" s="89" t="s">
-        <v>316</v>
+        <v>366</v>
       </c>
       <c r="L40" s="89" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="M40" s="89" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="N40" s="89"/>
       <c r="O40" s="89" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="P40" s="89" t="s">
-        <v>296</v>
+        <v>249</v>
       </c>
       <c r="Q40" s="89" t="s">
-        <v>297</v>
+        <v>349</v>
       </c>
       <c r="R40" s="89" t="s">
-        <v>275</v>
+        <v>354</v>
       </c>
       <c r="S40" s="53"/>
       <c r="V40" s="69"/>
@@ -5234,49 +5263,49 @@
       </c>
       <c r="C41" s="52"/>
       <c r="D41" s="72" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E41" s="72" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F41" s="72" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G41" s="72" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="H41" s="72" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I41" s="72" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="J41" s="72" t="s">
-        <v>195</v>
-      </c>
-      <c r="K41" s="105" t="s">
-        <v>241</v>
+        <v>194</v>
+      </c>
+      <c r="K41" s="99" t="s">
+        <v>353</v>
       </c>
       <c r="L41" s="72" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="M41" s="72" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="N41" s="72" t="s">
         <v>168</v>
       </c>
       <c r="O41" s="72" t="s">
-        <v>229</v>
-      </c>
-      <c r="P41" s="105" t="s">
-        <v>230</v>
+        <v>226</v>
+      </c>
+      <c r="P41" s="99" t="s">
+        <v>334</v>
       </c>
       <c r="Q41" s="72" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R41" s="72" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S41" s="54"/>
       <c r="V41" s="69"/>
@@ -5285,41 +5314,41 @@
       <c r="B42" s="67"/>
       <c r="C42" s="52"/>
       <c r="D42" s="94" t="s">
-        <v>354</v>
+        <v>326</v>
       </c>
       <c r="E42" s="94"/>
       <c r="F42" s="94" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="G42" s="94" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="H42" s="94"/>
       <c r="I42" s="94" t="s">
-        <v>361</v>
+        <v>332</v>
       </c>
       <c r="J42" s="94"/>
       <c r="K42" s="94" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="L42" s="94" t="s">
-        <v>355</v>
+        <v>327</v>
       </c>
       <c r="M42" s="94" t="s">
-        <v>356</v>
+        <v>328</v>
       </c>
       <c r="N42" s="94"/>
       <c r="O42" s="94" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="P42" s="94" t="s">
-        <v>351</v>
+        <v>311</v>
       </c>
       <c r="Q42" s="94" t="s">
-        <v>298</v>
+        <v>350</v>
       </c>
       <c r="R42" s="94" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="S42" s="58"/>
       <c r="V42" s="69"/>
@@ -5352,29 +5381,29 @@
       <c r="E44" s="89"/>
       <c r="F44" s="89"/>
       <c r="G44" s="89" t="s">
-        <v>275</v>
+        <v>343</v>
       </c>
       <c r="H44" s="89" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="I44" s="89"/>
       <c r="J44" s="89" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="K44" s="89" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="L44" s="89"/>
       <c r="M44" s="89"/>
       <c r="N44" s="89"/>
       <c r="O44" s="89" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="P44" s="89" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="Q44" s="89" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="R44" s="89"/>
       <c r="S44" s="53"/>
@@ -5387,49 +5416,49 @@
       </c>
       <c r="C45" s="52"/>
       <c r="D45" s="72" t="s">
+        <v>199</v>
+      </c>
+      <c r="E45" s="72" t="s">
         <v>200</v>
       </c>
-      <c r="E45" s="72" t="s">
-        <v>201</v>
-      </c>
       <c r="F45" s="72" t="s">
+        <v>191</v>
+      </c>
+      <c r="G45" s="72" t="s">
+        <v>221</v>
+      </c>
+      <c r="H45" s="72" t="s">
+        <v>233</v>
+      </c>
+      <c r="I45" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="J45" s="72" t="s">
+        <v>175</v>
+      </c>
+      <c r="K45" s="72" t="s">
+        <v>176</v>
+      </c>
+      <c r="L45" s="72" t="s">
         <v>192</v>
       </c>
-      <c r="G45" s="72" t="s">
-        <v>222</v>
-      </c>
-      <c r="H45" s="72" t="s">
-        <v>236</v>
-      </c>
-      <c r="I45" s="72" t="s">
-        <v>175</v>
-      </c>
-      <c r="J45" s="72" t="s">
-        <v>176</v>
-      </c>
-      <c r="K45" s="72" t="s">
-        <v>177</v>
-      </c>
-      <c r="L45" s="72" t="s">
-        <v>193</v>
-      </c>
       <c r="M45" s="72" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N45" s="72" t="s">
+        <v>191</v>
+      </c>
+      <c r="O45" s="72" t="s">
+        <v>188</v>
+      </c>
+      <c r="P45" s="72" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q45" s="72" t="s">
+        <v>190</v>
+      </c>
+      <c r="R45" s="72" t="s">
         <v>192</v>
-      </c>
-      <c r="O45" s="72" t="s">
-        <v>189</v>
-      </c>
-      <c r="P45" s="72" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q45" s="72" t="s">
-        <v>191</v>
-      </c>
-      <c r="R45" s="72" t="s">
-        <v>193</v>
       </c>
       <c r="S45" s="54"/>
       <c r="V45" s="69"/>
@@ -5441,29 +5470,29 @@
       <c r="E46" s="94"/>
       <c r="F46" s="94"/>
       <c r="G46" s="94" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="H46" s="94" t="s">
-        <v>357</v>
+        <v>329</v>
       </c>
       <c r="I46" s="94"/>
       <c r="J46" s="94" t="s">
-        <v>358</v>
+        <v>330</v>
       </c>
       <c r="K46" s="94" t="s">
-        <v>359</v>
+        <v>331</v>
       </c>
       <c r="L46" s="94"/>
       <c r="M46" s="94"/>
       <c r="N46" s="94"/>
       <c r="O46" s="94" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="P46" s="94" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="Q46" s="94" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="R46" s="94"/>
       <c r="S46" s="58"/>
@@ -5494,47 +5523,47 @@
       <c r="B48" s="65"/>
       <c r="C48" s="52"/>
       <c r="D48" s="89" t="s">
+        <v>250</v>
+      </c>
+      <c r="E48" s="89" t="s">
+        <v>254</v>
+      </c>
+      <c r="F48" s="89" t="s">
+        <v>357</v>
+      </c>
+      <c r="G48" s="89" t="s">
+        <v>305</v>
+      </c>
+      <c r="H48" s="89" t="s">
+        <v>269</v>
+      </c>
+      <c r="I48" s="89" t="s">
         <v>261</v>
       </c>
-      <c r="E48" s="89" t="s">
-        <v>265</v>
-      </c>
-      <c r="F48" s="89" t="s">
-        <v>253</v>
-      </c>
-      <c r="G48" s="89" t="s">
-        <v>329</v>
-      </c>
-      <c r="H48" s="89" t="s">
-        <v>284</v>
-      </c>
-      <c r="I48" s="89" t="s">
-        <v>272</v>
-      </c>
       <c r="J48" s="89" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="K48" s="89"/>
       <c r="L48" s="89" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="M48" s="89" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="N48" s="89" t="s">
-        <v>317</v>
+        <v>293</v>
       </c>
       <c r="O48" s="89" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="P48" s="89" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="Q48" s="89" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="R48" s="89" t="s">
-        <v>275</v>
+        <v>343</v>
       </c>
       <c r="S48" s="53"/>
       <c r="V48" s="69"/>
@@ -5546,49 +5575,49 @@
       </c>
       <c r="C49" s="52"/>
       <c r="D49" s="72" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E49" s="72" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F49" s="72" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G49" s="72" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H49" s="72" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I49" s="72" t="s">
+        <v>218</v>
+      </c>
+      <c r="J49" s="72" t="s">
         <v>219</v>
-      </c>
-      <c r="J49" s="72" t="s">
-        <v>220</v>
       </c>
       <c r="K49" s="72" t="s">
         <v>168</v>
       </c>
       <c r="L49" s="72" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M49" s="72" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="N49" s="72" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="O49" s="72" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P49" s="72" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q49" s="72" t="s">
         <v>172</v>
       </c>
-      <c r="Q49" s="72" t="s">
-        <v>173</v>
-      </c>
       <c r="R49" s="72" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S49" s="54"/>
       <c r="V49" s="69"/>
@@ -5597,47 +5626,47 @@
       <c r="B50" s="67"/>
       <c r="C50" s="52"/>
       <c r="D50" s="94" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="E50" s="94" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="F50" s="94" t="s">
-        <v>254</v>
+        <v>358</v>
       </c>
       <c r="G50" s="94" t="s">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="H50" s="94" t="s">
-        <v>347</v>
+        <v>320</v>
       </c>
       <c r="I50" s="94" t="s">
-        <v>338</v>
+        <v>313</v>
       </c>
       <c r="J50" s="94" t="s">
-        <v>339</v>
+        <v>314</v>
       </c>
       <c r="K50" s="94"/>
       <c r="L50" s="94" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="M50" s="94" t="s">
-        <v>326</v>
+        <v>302</v>
       </c>
       <c r="N50" s="94" t="s">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="O50" s="94" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="P50" s="94" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="Q50" s="94" t="s">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="R50" s="94" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="S50" s="58"/>
       <c r="V50" s="69"/>
@@ -5667,45 +5696,45 @@
       <c r="B52" s="65"/>
       <c r="C52" s="52"/>
       <c r="D52" s="89" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="E52" s="89" t="s">
-        <v>296</v>
+        <v>249</v>
       </c>
       <c r="F52" s="89" t="s">
-        <v>297</v>
+        <v>349</v>
       </c>
       <c r="G52" s="89"/>
       <c r="H52" s="89" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="I52" s="89" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="J52" s="89" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="K52" s="89"/>
       <c r="L52" s="89" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="M52" s="89" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="N52" s="89" t="s">
-        <v>319</v>
+        <v>295</v>
       </c>
       <c r="O52" s="89" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="P52" s="89" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="Q52" s="89" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="R52" s="89" t="s">
-        <v>321</v>
+        <v>297</v>
       </c>
       <c r="S52" s="53"/>
       <c r="V52" s="69"/>
@@ -5717,49 +5746,49 @@
       </c>
       <c r="C53" s="52"/>
       <c r="D53" s="72" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E53" s="72" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F53" s="72" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G53" s="72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H53" s="72" t="s">
+        <v>188</v>
+      </c>
+      <c r="I53" s="72" t="s">
         <v>189</v>
       </c>
-      <c r="I53" s="72" t="s">
+      <c r="J53" s="72" t="s">
         <v>190</v>
       </c>
-      <c r="J53" s="72" t="s">
-        <v>191</v>
-      </c>
       <c r="K53" s="72" t="s">
+        <v>192</v>
+      </c>
+      <c r="L53" s="72" t="s">
+        <v>189</v>
+      </c>
+      <c r="M53" s="72" t="s">
         <v>193</v>
       </c>
-      <c r="L53" s="72" t="s">
-        <v>190</v>
-      </c>
-      <c r="M53" s="72" t="s">
-        <v>194</v>
-      </c>
       <c r="N53" s="72" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="O53" s="72" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P53" s="72" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q53" s="72" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R53" s="72" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="S53" s="54"/>
       <c r="V53" s="69"/>
@@ -5768,45 +5797,45 @@
       <c r="B54" s="67"/>
       <c r="C54" s="52"/>
       <c r="D54" s="94" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="E54" s="94" t="s">
-        <v>351</v>
+        <v>311</v>
       </c>
       <c r="F54" s="94" t="s">
-        <v>298</v>
+        <v>350</v>
       </c>
       <c r="G54" s="94"/>
       <c r="H54" s="94" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="I54" s="94" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="J54" s="94" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="K54" s="94"/>
       <c r="L54" s="94" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="M54" s="94" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="N54" s="94" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="O54" s="94" t="s">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="P54" s="94" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="Q54" s="94" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="R54" s="94" t="s">
-        <v>363</v>
+        <v>333</v>
       </c>
       <c r="S54" s="58"/>
       <c r="V54" s="69"/>
@@ -5836,7 +5865,7 @@
       <c r="B56" s="65"/>
       <c r="C56" s="52"/>
       <c r="D56" s="89" t="s">
-        <v>329</v>
+        <v>305</v>
       </c>
       <c r="E56" s="89"/>
       <c r="F56" s="89"/>
@@ -5862,13 +5891,13 @@
       </c>
       <c r="C57" s="52"/>
       <c r="D57" s="72" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E57" s="72" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F57" s="72" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G57" s="72"/>
       <c r="H57" s="72"/>
@@ -5889,7 +5918,7 @@
       <c r="B58" s="67"/>
       <c r="C58" s="52"/>
       <c r="D58" s="94" t="s">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="E58" s="94"/>
       <c r="F58" s="94"/>
@@ -6068,7 +6097,7 @@
       </c>
     </row>
     <row r="5" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B5" s="102" t="s">
+      <c r="B5" s="104" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
@@ -6086,7 +6115,7 @@
       <c r="G5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="102" t="s">
+      <c r="I5" s="104" t="s">
         <v>6</v>
       </c>
       <c r="J5" s="6" t="s">
@@ -6111,7 +6140,7 @@
       <c r="R5" s="10"/>
     </row>
     <row r="6" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B6" s="103"/>
+      <c r="B6" s="105"/>
       <c r="C6" s="11" t="s">
         <v>16</v>
       </c>
@@ -6131,7 +6160,7 @@
         <f>$B5 &amp; G$4</f>
         <v>陰入</v>
       </c>
-      <c r="I6" s="103"/>
+      <c r="I6" s="105"/>
       <c r="J6" s="11" t="s">
         <v>17</v>
       </c>
@@ -6153,7 +6182,7 @@
       <c r="Q6" s="14"/>
     </row>
     <row r="7" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B7" s="103"/>
+      <c r="B7" s="105"/>
       <c r="C7" s="15" t="s">
         <v>22</v>
       </c>
@@ -6169,7 +6198,7 @@
       <c r="G7" s="16">
         <v>30</v>
       </c>
-      <c r="I7" s="103"/>
+      <c r="I7" s="105"/>
       <c r="J7" s="15" t="s">
         <v>22</v>
       </c>
@@ -6191,7 +6220,7 @@
       <c r="Q7" s="14"/>
     </row>
     <row r="8" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B8" s="103"/>
+      <c r="B8" s="105"/>
       <c r="C8" s="11" t="s">
         <v>24</v>
       </c>
@@ -6207,7 +6236,7 @@
       <c r="G8" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="103"/>
+      <c r="I8" s="105"/>
       <c r="J8" s="18" t="s">
         <v>24</v>
       </c>
@@ -6229,7 +6258,7 @@
       <c r="Q8" s="14"/>
     </row>
     <row r="9" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B9" s="103"/>
+      <c r="B9" s="105"/>
       <c r="C9" s="11" t="s">
         <v>33</v>
       </c>
@@ -6245,7 +6274,7 @@
       <c r="G9" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="I9" s="103"/>
+      <c r="I9" s="105"/>
       <c r="J9" s="11" t="s">
         <v>33</v>
       </c>
@@ -6267,7 +6296,7 @@
       <c r="Q9" s="14"/>
     </row>
     <row r="10" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B10" s="104"/>
+      <c r="B10" s="106"/>
       <c r="C10" s="11" t="s">
         <v>38</v>
       </c>
@@ -6283,7 +6312,7 @@
       <c r="G10" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="I10" s="104"/>
+      <c r="I10" s="106"/>
       <c r="J10" s="11" t="s">
         <v>43</v>
       </c>
@@ -6306,7 +6335,7 @@
       <c r="R10" s="28"/>
     </row>
     <row r="11" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B11" s="102" t="s">
+      <c r="B11" s="104" t="s">
         <v>48</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -6324,7 +6353,7 @@
       <c r="G11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="I11" s="102" t="s">
+      <c r="I11" s="104" t="s">
         <v>48</v>
       </c>
       <c r="J11" s="6" t="s">
@@ -6348,7 +6377,7 @@
       <c r="Q11" s="14"/>
     </row>
     <row r="12" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B12" s="103"/>
+      <c r="B12" s="105"/>
       <c r="C12" s="11" t="s">
         <v>16</v>
       </c>
@@ -6368,7 +6397,7 @@
         <f>$B11 &amp; G$4</f>
         <v>陽入</v>
       </c>
-      <c r="I12" s="103"/>
+      <c r="I12" s="105"/>
       <c r="J12" s="11" t="s">
         <v>17</v>
       </c>
@@ -6388,7 +6417,7 @@
       <c r="Q12" s="14"/>
     </row>
     <row r="13" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B13" s="103"/>
+      <c r="B13" s="105"/>
       <c r="C13" s="15" t="s">
         <v>22</v>
       </c>
@@ -6402,7 +6431,7 @@
       <c r="G13" s="16">
         <v>50</v>
       </c>
-      <c r="I13" s="103"/>
+      <c r="I13" s="105"/>
       <c r="J13" s="15" t="s">
         <v>22</v>
       </c>
@@ -6422,7 +6451,7 @@
       <c r="Q13" s="14"/>
     </row>
     <row r="14" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B14" s="103"/>
+      <c r="B14" s="105"/>
       <c r="C14" s="11" t="s">
         <v>24</v>
       </c>
@@ -6436,7 +6465,7 @@
       <c r="G14" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="I14" s="103"/>
+      <c r="I14" s="105"/>
       <c r="J14" s="11" t="s">
         <v>24</v>
       </c>
@@ -6456,7 +6485,7 @@
       <c r="Q14" s="14"/>
     </row>
     <row r="15" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B15" s="103"/>
+      <c r="B15" s="105"/>
       <c r="C15" s="11" t="s">
         <v>33</v>
       </c>
@@ -6470,7 +6499,7 @@
       <c r="G15" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="I15" s="103"/>
+      <c r="I15" s="105"/>
       <c r="J15" s="11" t="s">
         <v>33</v>
       </c>
@@ -6490,7 +6519,7 @@
       <c r="Q15" s="14"/>
     </row>
     <row r="16" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B16" s="104"/>
+      <c r="B16" s="106"/>
       <c r="C16" s="11" t="s">
         <v>38</v>
       </c>
@@ -6504,7 +6533,7 @@
       <c r="G16" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="I16" s="104"/>
+      <c r="I16" s="106"/>
       <c r="J16" s="11" t="s">
         <v>43</v>
       </c>
@@ -6543,7 +6572,7 @@
         <v>1</v>
       </c>
       <c r="K19" s="91" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L19" s="37"/>
       <c r="M19" s="37"/>
@@ -6555,7 +6584,7 @@
         <v>7</v>
       </c>
       <c r="K20" s="91" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L20" s="37"/>
       <c r="M20" s="37"/>
@@ -6567,7 +6596,7 @@
         <v>3</v>
       </c>
       <c r="K21" s="91" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L21" s="37"/>
       <c r="M21" s="37"/>
@@ -6579,7 +6608,7 @@
         <v>2</v>
       </c>
       <c r="K22" s="92" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L22" s="37"/>
       <c r="M22" s="37"/>
@@ -6591,7 +6620,7 @@
         <v>5</v>
       </c>
       <c r="K23" s="92" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L23" s="37"/>
       <c r="M23" s="37"/>
@@ -6600,10 +6629,10 @@
     <row r="24" spans="3:14" ht="42.75" customHeight="1">
       <c r="C24" s="36"/>
       <c r="J24" s="90" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K24" s="93" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L24" s="37"/>
       <c r="M24" s="37"/>
@@ -6615,7 +6644,7 @@
         <v>4</v>
       </c>
       <c r="K25" s="91" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L25" s="37"/>
       <c r="M25" s="37"/>
@@ -6627,7 +6656,7 @@
         <v>8</v>
       </c>
       <c r="K26" s="91" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L26" s="37"/>
       <c r="M26" s="37"/>
@@ -6774,13 +6803,13 @@
         <v>81</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G4" s="45" t="s">
         <v>82</v>
       </c>
       <c r="H4" s="44" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J4" s="40" t="s">
         <v>83</v>
@@ -6844,13 +6873,13 @@
         <v>93</v>
       </c>
       <c r="F8" s="44" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G8" s="45" t="s">
         <v>82</v>
       </c>
       <c r="H8" s="44" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J8" s="40" t="s">
         <v>94</v>
@@ -6911,13 +6940,13 @@
         <v>104</v>
       </c>
       <c r="F12" s="44" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G12" s="45" t="s">
         <v>82</v>
       </c>
       <c r="H12" s="44" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J12" s="40" t="s">
         <v>105</v>
@@ -6978,13 +7007,13 @@
         <v>115</v>
       </c>
       <c r="F16" s="44" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G16" s="45" t="s">
         <v>82</v>
       </c>
       <c r="H16" s="44" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J16" s="40" t="s">
         <v>116</v>
@@ -7045,13 +7074,13 @@
         <v>127</v>
       </c>
       <c r="F20" s="44" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G20" s="45" t="s">
         <v>82</v>
       </c>
       <c r="H20" s="44" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J20" s="40" t="s">
         <v>128</v>

--- a/output2/【河洛話注音】金剛般若波羅蜜經004。妙行無住分第四.xlsx
+++ b/output2/【河洛話注音】金剛般若波羅蜜經004。妙行無住分第四.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F4FDF6D-6DAD-4B86-BB16-749AFBA42DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60A49C9C-36BF-4445-A8BF-C02F2371DEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28545" yWindow="405" windowWidth="27645" windowHeight="15585" activeTab="1" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
   </bookViews>
@@ -1405,10 +1405,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>siann1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>bi7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1521,14 +1517,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>iah8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㄚㆷ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>tan6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1621,10 +1609,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄒㄧㆩˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ㆠㄧ˫</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1818,6 +1802,22 @@
   </si>
   <si>
     <t>ㄏㄚ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sing1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㄥˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ik8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㆻ˙</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3773,13 +3773,13 @@
         <v>244</v>
       </c>
       <c r="E4" s="89" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="F4" s="89" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="G4" s="89" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H4" s="89" t="s">
         <v>245</v>
@@ -3788,7 +3788,7 @@
         <v>246</v>
       </c>
       <c r="J4" s="89" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="K4" s="89"/>
       <c r="L4" s="89"/>
@@ -3812,7 +3812,7 @@
         <v>212</v>
       </c>
       <c r="F5" s="100" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="G5" s="72" t="s">
         <v>198</v>
@@ -3824,7 +3824,7 @@
         <v>170</v>
       </c>
       <c r="J5" s="99" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="K5" s="72"/>
       <c r="L5" s="72"/>
@@ -3841,25 +3841,25 @@
       <c r="B6" s="67"/>
       <c r="C6" s="51"/>
       <c r="D6" s="94" t="s">
+        <v>301</v>
+      </c>
+      <c r="E6" s="94" t="s">
+        <v>336</v>
+      </c>
+      <c r="F6" s="94" t="s">
+        <v>354</v>
+      </c>
+      <c r="G6" s="94" t="s">
+        <v>303</v>
+      </c>
+      <c r="H6" s="94" t="s">
         <v>304</v>
       </c>
-      <c r="E6" s="94" t="s">
-        <v>340</v>
-      </c>
-      <c r="F6" s="94" t="s">
-        <v>358</v>
-      </c>
-      <c r="G6" s="94" t="s">
-        <v>306</v>
-      </c>
-      <c r="H6" s="94" t="s">
-        <v>307</v>
-      </c>
       <c r="I6" s="94" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="J6" s="94" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="K6" s="94"/>
       <c r="L6" s="94"/>
@@ -3900,7 +3900,7 @@
         <v>247</v>
       </c>
       <c r="E8" s="89" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F8" s="89"/>
       <c r="G8" s="89"/>
@@ -3921,7 +3921,7 @@
         <v>254</v>
       </c>
       <c r="N8" s="89" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="O8" s="89" t="s">
         <v>256</v>
@@ -3931,7 +3931,7 @@
         <v>258</v>
       </c>
       <c r="R8" s="89" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="S8" s="53"/>
       <c r="V8" s="102"/>
@@ -3998,12 +3998,12 @@
         <v>248</v>
       </c>
       <c r="E10" s="94" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F10" s="94"/>
       <c r="G10" s="94"/>
       <c r="H10" s="94" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="I10" s="94" t="s">
         <v>251</v>
@@ -4019,17 +4019,17 @@
         <v>255</v>
       </c>
       <c r="N10" s="94" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="O10" s="94" t="s">
         <v>257</v>
       </c>
       <c r="P10" s="94"/>
       <c r="Q10" s="94" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="R10" s="94" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="S10" s="58"/>
       <c r="V10" s="102"/>
@@ -4062,14 +4062,14 @@
         <v>259</v>
       </c>
       <c r="E12" s="89" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F12" s="89"/>
       <c r="G12" s="89" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H12" s="89" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I12" s="89" t="s">
         <v>261</v>
@@ -4085,13 +4085,13 @@
         <v>263</v>
       </c>
       <c r="N12" s="89" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="O12" s="89" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="P12" s="89" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="Q12" s="89" t="s">
         <v>261</v>
@@ -4163,42 +4163,42 @@
         <v>260</v>
       </c>
       <c r="E14" s="94" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F14" s="94"/>
       <c r="G14" s="94" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H14" s="94" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="I14" s="94" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="J14" s="94" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K14" s="94"/>
       <c r="L14" s="94" t="s">
         <v>260</v>
       </c>
       <c r="M14" s="94" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="N14" s="94" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="O14" s="94" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="P14" s="94" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Q14" s="94" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="R14" s="94" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="S14" s="58"/>
       <c r="V14" s="69"/>
@@ -4229,25 +4229,25 @@
       <c r="C16" s="52"/>
       <c r="D16" s="89"/>
       <c r="E16" s="89" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="F16" s="89" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G16" s="89" t="s">
-        <v>264</v>
+        <v>364</v>
       </c>
       <c r="H16" s="89"/>
       <c r="I16" s="89" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="J16" s="89"/>
       <c r="K16" s="89" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L16" s="89"/>
       <c r="M16" s="89" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="N16" s="89"/>
       <c r="O16" s="89" t="s">
@@ -4285,7 +4285,7 @@
         <v>194</v>
       </c>
       <c r="I17" s="99" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="J17" s="72" t="s">
         <v>194</v>
@@ -4297,7 +4297,7 @@
         <v>194</v>
       </c>
       <c r="M17" s="99" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="N17" s="72" t="s">
         <v>194</v>
@@ -4322,35 +4322,35 @@
       <c r="C18" s="52"/>
       <c r="D18" s="94"/>
       <c r="E18" s="94" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F18" s="94" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G18" s="94" t="s">
-        <v>318</v>
+        <v>365</v>
       </c>
       <c r="H18" s="94"/>
       <c r="I18" s="94" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="J18" s="94"/>
       <c r="K18" s="94" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="L18" s="94"/>
       <c r="M18" s="94" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="N18" s="94"/>
       <c r="O18" s="94" t="s">
         <v>257</v>
       </c>
       <c r="P18" s="94" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="Q18" s="94" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="R18" s="94"/>
       <c r="S18" s="58"/>
@@ -4400,10 +4400,10 @@
         <v>258</v>
       </c>
       <c r="K20" s="89" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L20" s="89" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="M20" s="89" t="s">
         <v>261</v>
@@ -4413,13 +4413,13 @@
       </c>
       <c r="O20" s="89"/>
       <c r="P20" s="89" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="Q20" s="89" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="R20" s="89" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="S20" s="53"/>
       <c r="V20" s="69"/>
@@ -4482,7 +4482,7 @@
       <c r="B22" s="67"/>
       <c r="C22" s="52"/>
       <c r="D22" s="94" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="E22" s="94" t="s">
         <v>251</v>
@@ -4498,29 +4498,29 @@
         <v>255</v>
       </c>
       <c r="J22" s="94" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K22" s="94" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L22" s="94" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="M22" s="94" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N22" s="94" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="O22" s="94"/>
       <c r="P22" s="94" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="Q22" s="94" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="R22" s="94" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="S22" s="58"/>
       <c r="V22" s="69"/>
@@ -4550,21 +4550,21 @@
       <c r="B24" s="65"/>
       <c r="C24" s="52"/>
       <c r="D24" s="89" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E24" s="89"/>
       <c r="F24" s="89" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G24" s="89" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H24" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I24" s="89"/>
       <c r="J24" s="89" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="K24" s="89" t="s">
         <v>250</v>
@@ -4573,13 +4573,13 @@
         <v>254</v>
       </c>
       <c r="M24" s="89" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="N24" s="89" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="O24" s="89" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P24" s="89" t="s">
         <v>261</v>
@@ -4616,7 +4616,7 @@
         <v>199</v>
       </c>
       <c r="J25" s="100" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="K25" s="72" t="s">
         <v>189</v>
@@ -4649,21 +4649,21 @@
       <c r="B26" s="67"/>
       <c r="C26" s="52"/>
       <c r="D26" s="94" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E26" s="94"/>
       <c r="F26" s="94" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="G26" s="94" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H26" s="94" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="I26" s="94"/>
       <c r="J26" s="94" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="K26" s="94" t="s">
         <v>251</v>
@@ -4672,19 +4672,19 @@
         <v>255</v>
       </c>
       <c r="M26" s="94" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="N26" s="94" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="O26" s="94" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="P26" s="94" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="Q26" s="94" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="R26" s="94"/>
       <c r="S26" s="58"/>
@@ -4723,25 +4723,25 @@
       <c r="B28" s="65"/>
       <c r="C28" s="52"/>
       <c r="D28" s="89" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E28" s="89" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F28" s="89" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G28" s="89" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="H28" s="89" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I28" s="89" t="s">
         <v>249</v>
       </c>
       <c r="J28" s="89" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="K28" s="89"/>
       <c r="L28" s="89" t="s">
@@ -4755,13 +4755,13 @@
       </c>
       <c r="O28" s="89"/>
       <c r="P28" s="89" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="Q28" s="89" t="s">
+        <v>278</v>
+      </c>
+      <c r="R28" s="89" t="s">
         <v>279</v>
-      </c>
-      <c r="R28" s="89" t="s">
-        <v>280</v>
       </c>
       <c r="S28" s="53"/>
       <c r="U28" s="1" t="e">
@@ -4792,10 +4792,10 @@
         <v>226</v>
       </c>
       <c r="I29" s="99" t="s">
+        <v>330</v>
+      </c>
+      <c r="J29" s="99" t="s">
         <v>334</v>
-      </c>
-      <c r="J29" s="99" t="s">
-        <v>338</v>
       </c>
       <c r="K29" s="72" t="s">
         <v>174</v>
@@ -4832,29 +4832,29 @@
       <c r="B30" s="67"/>
       <c r="C30" s="52"/>
       <c r="D30" s="94" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E30" s="94" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F30" s="94" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G30" s="94" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="H30" s="94" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I30" s="94" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="J30" s="94" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="K30" s="94"/>
       <c r="L30" s="94" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="M30" s="94" t="s">
         <v>251</v>
@@ -4864,13 +4864,13 @@
       </c>
       <c r="O30" s="94"/>
       <c r="P30" s="94" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="Q30" s="94" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="R30" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="S30" s="58"/>
       <c r="U30" s="1" t="s">
@@ -4891,7 +4891,7 @@
       <c r="K31" s="79"/>
       <c r="L31" s="79"/>
       <c r="M31" s="79" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="N31" s="79"/>
       <c r="O31" s="79"/>
@@ -4905,41 +4905,41 @@
       <c r="B32" s="65"/>
       <c r="C32" s="52"/>
       <c r="D32" s="89" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E32" s="89"/>
       <c r="F32" s="89" t="s">
+        <v>281</v>
+      </c>
+      <c r="G32" s="89" t="s">
         <v>282</v>
       </c>
-      <c r="G32" s="89" t="s">
+      <c r="H32" s="89" t="s">
         <v>283</v>
       </c>
-      <c r="H32" s="89" t="s">
+      <c r="I32" s="89" t="s">
         <v>284</v>
       </c>
-      <c r="I32" s="89" t="s">
-        <v>285</v>
-      </c>
       <c r="J32" s="89" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K32" s="89" t="s">
         <v>249</v>
       </c>
       <c r="L32" s="89" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="M32" s="89" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="N32" s="89"/>
       <c r="O32" s="89"/>
       <c r="P32" s="89"/>
       <c r="Q32" s="89" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="R32" s="89" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S32" s="53"/>
       <c r="V32" s="69"/>
@@ -5002,41 +5002,41 @@
       <c r="B34" s="67"/>
       <c r="C34" s="52"/>
       <c r="D34" s="94" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E34" s="94"/>
       <c r="F34" s="94" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="G34" s="94" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H34" s="94" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="I34" s="94" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="J34" s="94" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K34" s="94" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="L34" s="94" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="M34" s="94" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="N34" s="94"/>
       <c r="O34" s="94"/>
       <c r="P34" s="94"/>
       <c r="Q34" s="94" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="R34" s="94" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="S34" s="58"/>
       <c r="V34" s="69"/>
@@ -5067,10 +5067,10 @@
       <c r="C36" s="52"/>
       <c r="D36" s="89"/>
       <c r="E36" s="89" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F36" s="89" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G36" s="89"/>
       <c r="H36" s="89"/>
@@ -5086,15 +5086,15 @@
       </c>
       <c r="M36" s="89"/>
       <c r="N36" s="89" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="O36" s="89"/>
       <c r="P36" s="89" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="Q36" s="89"/>
       <c r="R36" s="89" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="S36" s="53"/>
       <c r="V36" s="69"/>
@@ -5142,13 +5142,13 @@
         <v>194</v>
       </c>
       <c r="P37" s="99" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="Q37" s="72" t="s">
         <v>194</v>
       </c>
       <c r="R37" s="99" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="S37" s="54"/>
       <c r="V37" s="69"/>
@@ -5158,16 +5158,16 @@
       <c r="C38" s="52"/>
       <c r="D38" s="94"/>
       <c r="E38" s="94" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="F38" s="94" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G38" s="94"/>
       <c r="H38" s="94"/>
       <c r="I38" s="94"/>
       <c r="J38" s="94" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="K38" s="94" t="s">
         <v>251</v>
@@ -5177,15 +5177,15 @@
       </c>
       <c r="M38" s="94"/>
       <c r="N38" s="94" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O38" s="94"/>
       <c r="P38" s="94" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="Q38" s="94"/>
       <c r="R38" s="94" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="S38" s="58"/>
       <c r="V38" s="69"/>
@@ -5208,7 +5208,7 @@
       <c r="P39" s="79"/>
       <c r="Q39" s="79"/>
       <c r="R39" s="79" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="S39" s="85"/>
       <c r="V39" s="87"/>
@@ -5217,41 +5217,41 @@
       <c r="B40" s="65"/>
       <c r="C40" s="52"/>
       <c r="D40" s="89" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E40" s="89"/>
       <c r="F40" s="89" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="G40" s="89" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H40" s="89"/>
       <c r="I40" s="89" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J40" s="89"/>
       <c r="K40" s="89" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="L40" s="89" t="s">
+        <v>283</v>
+      </c>
+      <c r="M40" s="89" t="s">
         <v>284</v>
-      </c>
-      <c r="M40" s="89" t="s">
-        <v>285</v>
       </c>
       <c r="N40" s="89"/>
       <c r="O40" s="89" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P40" s="89" t="s">
         <v>249</v>
       </c>
       <c r="Q40" s="89" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="R40" s="89" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="S40" s="53"/>
       <c r="V40" s="69"/>
@@ -5284,7 +5284,7 @@
         <v>194</v>
       </c>
       <c r="K41" s="99" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="L41" s="72" t="s">
         <v>231</v>
@@ -5299,7 +5299,7 @@
         <v>226</v>
       </c>
       <c r="P41" s="99" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="Q41" s="72" t="s">
         <v>206</v>
@@ -5314,41 +5314,41 @@
       <c r="B42" s="67"/>
       <c r="C42" s="52"/>
       <c r="D42" s="94" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E42" s="94"/>
       <c r="F42" s="94" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="G42" s="94" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H42" s="94"/>
       <c r="I42" s="94" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="J42" s="94"/>
       <c r="K42" s="94" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="L42" s="94" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="M42" s="94" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="N42" s="94"/>
       <c r="O42" s="94" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P42" s="94" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="Q42" s="94" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="R42" s="94" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="S42" s="58"/>
       <c r="V42" s="69"/>
@@ -5381,17 +5381,17 @@
       <c r="E44" s="89"/>
       <c r="F44" s="89"/>
       <c r="G44" s="89" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="H44" s="89" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I44" s="89"/>
       <c r="J44" s="89" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K44" s="89" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="L44" s="89"/>
       <c r="M44" s="89"/>
@@ -5470,23 +5470,23 @@
       <c r="E46" s="94"/>
       <c r="F46" s="94"/>
       <c r="G46" s="94" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="H46" s="94" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="I46" s="94"/>
       <c r="J46" s="94" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="K46" s="94" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="L46" s="94"/>
       <c r="M46" s="94"/>
       <c r="N46" s="94"/>
       <c r="O46" s="94" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="P46" s="94" t="s">
         <v>251</v>
@@ -5529,13 +5529,13 @@
         <v>254</v>
       </c>
       <c r="F48" s="89" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="G48" s="89" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H48" s="89" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I48" s="89" t="s">
         <v>261</v>
@@ -5545,25 +5545,25 @@
       </c>
       <c r="K48" s="89"/>
       <c r="L48" s="89" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="M48" s="89" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="N48" s="89" t="s">
-        <v>293</v>
+        <v>366</v>
       </c>
       <c r="O48" s="89" t="s">
         <v>247</v>
       </c>
       <c r="P48" s="89" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q48" s="89" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="R48" s="89" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="S48" s="53"/>
       <c r="V48" s="69"/>
@@ -5632,41 +5632,41 @@
         <v>255</v>
       </c>
       <c r="F50" s="94" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="G50" s="94" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="H50" s="94" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="I50" s="94" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="J50" s="94" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K50" s="94"/>
       <c r="L50" s="94" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M50" s="94" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="N50" s="94" t="s">
-        <v>294</v>
+        <v>367</v>
       </c>
       <c r="O50" s="94" t="s">
         <v>248</v>
       </c>
       <c r="P50" s="94" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q50" s="94" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="R50" s="94" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="S50" s="58"/>
       <c r="V50" s="69"/>
@@ -5696,13 +5696,13 @@
       <c r="B52" s="65"/>
       <c r="C52" s="52"/>
       <c r="D52" s="89" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E52" s="89" t="s">
         <v>249</v>
       </c>
       <c r="F52" s="89" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="G52" s="89"/>
       <c r="H52" s="89" t="s">
@@ -5722,19 +5722,19 @@
         <v>254</v>
       </c>
       <c r="N52" s="89" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="O52" s="89" t="s">
         <v>258</v>
       </c>
       <c r="P52" s="89" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q52" s="89" t="s">
         <v>259</v>
       </c>
       <c r="R52" s="89" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="S52" s="53"/>
       <c r="V52" s="69"/>
@@ -5797,17 +5797,17 @@
       <c r="B54" s="67"/>
       <c r="C54" s="52"/>
       <c r="D54" s="94" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E54" s="94" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F54" s="94" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="G54" s="94"/>
       <c r="H54" s="94" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="I54" s="94" t="s">
         <v>251</v>
@@ -5823,19 +5823,19 @@
         <v>255</v>
       </c>
       <c r="N54" s="94" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="O54" s="94" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="P54" s="94" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q54" s="94" t="s">
         <v>260</v>
       </c>
       <c r="R54" s="94" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="S54" s="58"/>
       <c r="V54" s="69"/>
@@ -5865,7 +5865,7 @@
       <c r="B56" s="65"/>
       <c r="C56" s="52"/>
       <c r="D56" s="89" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E56" s="89"/>
       <c r="F56" s="89"/>
@@ -5918,7 +5918,7 @@
       <c r="B58" s="67"/>
       <c r="C58" s="52"/>
       <c r="D58" s="94" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E58" s="94"/>
       <c r="F58" s="94"/>

--- a/output2/【河洛話注音】金剛般若波羅蜜經004。妙行無住分第四.xlsx
+++ b/output2/【河洛話注音】金剛般若波羅蜜經004。妙行無住分第四.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3201CA81-B04F-452E-AD16-957C8A243347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C184A5-0ACB-4D1D-9A2D-D2F0F86AF570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="10" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="366">
   <si>
     <t>【台羅拼音】</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1193,231 +1193,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>bu5</t>
-  </si>
-  <si>
-    <t>ㆠㄨˊ</t>
-  </si>
-  <si>
-    <t>hun1</t>
-  </si>
-  <si>
-    <t>ㄏㄨㄣˉ</t>
-  </si>
-  <si>
-    <t>te7</t>
-  </si>
-  <si>
-    <t>ㄉㆤ˫</t>
-  </si>
-  <si>
-    <t>su1</t>
-  </si>
-  <si>
-    <t>ㄙㄨˉ</t>
-  </si>
-  <si>
-    <t>phoo5</t>
-  </si>
-  <si>
-    <t>ㄆㆦˊ</t>
-  </si>
-  <si>
-    <t>the5</t>
-  </si>
-  <si>
-    <t>ㄊㆤˊ</t>
-  </si>
-  <si>
-    <t>se3</t>
-  </si>
-  <si>
-    <t>ㄙㆤ˪</t>
-  </si>
-  <si>
-    <t>zun1</t>
-  </si>
-  <si>
-    <t>ㄗㄨㄣˉ</t>
-  </si>
-  <si>
-    <t>lam5</t>
-  </si>
-  <si>
-    <t>ㄌㆰˊ</t>
-  </si>
-  <si>
-    <t>huat4</t>
-  </si>
-  <si>
-    <t>ㄏㄨㄚㆵ</t>
-  </si>
-  <si>
-    <t>un5</t>
-  </si>
-  <si>
-    <t>ㄨㄣˊ</t>
-  </si>
-  <si>
-    <t>ho5</t>
-  </si>
-  <si>
-    <t>ㄏㄜˊ</t>
-  </si>
-  <si>
-    <t>in3</t>
-  </si>
-  <si>
-    <t>ㄧㄣ˪</t>
-  </si>
-  <si>
-    <t>zu7</t>
-  </si>
-  <si>
-    <t>ㄗㄨ˫</t>
-  </si>
-  <si>
-    <t>hok8</t>
-  </si>
-  <si>
-    <t>ㄏㆦㆻ˙</t>
-  </si>
-  <si>
-    <t>ki5</t>
-  </si>
-  <si>
-    <t>ㄍㄧˊ</t>
-  </si>
-  <si>
-    <t>sing1</t>
-  </si>
-  <si>
-    <t>ㄒㄧㄥˉ</t>
-  </si>
-  <si>
-    <t>ju5</t>
-  </si>
-  <si>
-    <t>ㆡㄨˊ</t>
-  </si>
-  <si>
-    <t>si6</t>
-  </si>
-  <si>
-    <t>ㄒㄧˋ</t>
-  </si>
-  <si>
-    <t>i2</t>
-  </si>
-  <si>
-    <t>ㄧˋ</t>
-  </si>
-  <si>
-    <t>koo3</t>
-  </si>
-  <si>
-    <t>ㄍㆦ˪</t>
-  </si>
-  <si>
-    <t>jiok8</t>
-  </si>
-  <si>
-    <t>ㆢㄧㆦㆻ˙</t>
-  </si>
-  <si>
-    <t>sat4</t>
-  </si>
-  <si>
-    <t>ㄙㄚㆵ</t>
-  </si>
-  <si>
-    <t>siong3</t>
-  </si>
-  <si>
-    <t>ㄒㄧㆲ˪</t>
-  </si>
-  <si>
-    <t>soo2</t>
-  </si>
-  <si>
-    <t>ㄙㆦˋ</t>
-  </si>
-  <si>
-    <t>u5</t>
-  </si>
-  <si>
-    <t>ㄨˊ</t>
-  </si>
-  <si>
-    <t>i3</t>
-  </si>
-  <si>
-    <t>ㄧ˪</t>
-  </si>
-  <si>
-    <t>put4</t>
-  </si>
-  <si>
-    <t>ㄅㄨㆵ</t>
-  </si>
-  <si>
-    <t>ia7</t>
-  </si>
-  <si>
-    <t>ㄧㄚ˫</t>
-  </si>
-  <si>
-    <t>sik4</t>
-  </si>
-  <si>
-    <t>ㄒㄧㆻ</t>
-  </si>
-  <si>
-    <t>hi1</t>
-  </si>
-  <si>
-    <t>ㄏㄧˉ</t>
-  </si>
-  <si>
-    <t>ik8</t>
-  </si>
-  <si>
-    <t>ㄧㆻ˙</t>
-  </si>
-  <si>
-    <t>liong7</t>
-  </si>
-  <si>
-    <t>ㄌㄧㆲ˫</t>
-  </si>
-  <si>
     <t>hiu2</t>
   </si>
   <si>
     <t>可</t>
   </si>
   <si>
-    <t>hing5</t>
-  </si>
-  <si>
-    <t>ㄏㄧㄥˊ</t>
-  </si>
-  <si>
-    <t>kho2</t>
-  </si>
-  <si>
-    <t>ㄎㄜˋ</t>
-  </si>
-  <si>
-    <t>bi7</t>
-  </si>
-  <si>
-    <t>ㆠㄧ˫</t>
-  </si>
-  <si>
-    <t>ㄏㄧㄨˋ</t>
-  </si>
-  <si>
     <t>布</t>
   </si>
   <si>
@@ -1430,42 +1211,12 @@
     <t>德</t>
   </si>
   <si>
-    <t>poo3</t>
-  </si>
-  <si>
-    <t>ㄅㆦ˪</t>
-  </si>
-  <si>
-    <t>si1</t>
-  </si>
-  <si>
-    <t>ㄒㄧˉ</t>
-  </si>
-  <si>
-    <t>hok4</t>
-  </si>
-  <si>
-    <t>ㄏㆦㆻ</t>
-  </si>
-  <si>
-    <t>tik4</t>
-  </si>
-  <si>
-    <t>ㄉㄧㆻ</t>
-  </si>
-  <si>
     <t>色</t>
   </si>
   <si>
     <t>謂</t>
   </si>
   <si>
-    <t>ui7</t>
-  </si>
-  <si>
-    <t>ㄨㄧ˫</t>
-  </si>
-  <si>
     <t>行</t>
   </si>
   <si>
@@ -1478,43 +1229,13 @@
     <t>下</t>
   </si>
   <si>
-    <t>cu3</t>
-  </si>
-  <si>
-    <t>ㄘㄨ˪</t>
-  </si>
-  <si>
-    <t>ha7</t>
-  </si>
-  <si>
-    <t>ㄏㄚ˫</t>
-  </si>
-  <si>
     <t>四</t>
   </si>
   <si>
-    <t>su3</t>
-  </si>
-  <si>
-    <t>ㄙㄨ˪</t>
-  </si>
-  <si>
     <t>聲</t>
   </si>
   <si>
     <t>但</t>
-  </si>
-  <si>
-    <t>tan6</t>
-  </si>
-  <si>
-    <t>ㄉㄢˋ</t>
-  </si>
-  <si>
-    <t>i5</t>
-  </si>
-  <si>
-    <t>ㄧˊ</t>
   </si>
   <si>
     <t>妙行無住分第四
@@ -1565,63 +1286,459 @@
   </si>
   <si>
     <t>biau7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ㆠㄧㄠ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hing5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄧㄥˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bu5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆠㄨˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tsu7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗㄨ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hun1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄨㄣˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>te7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㆤ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>su3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄨ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hok8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㆦㆻ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tshu3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄘㄨ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>su1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄨˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>phoo1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄆㆦˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>the5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄊㆤˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sat4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄚㆵ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄨˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>huat4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄨㄚㆵ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ing1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㄥˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>soo2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㆦˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>poo3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄅㆦ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>si1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄨㄧ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>put4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄅㄨㆵ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sik4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sing1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㄥˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>hiong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ㄏㄧㆲˉ</t>
-  </si>
-  <si>
-    <t>ciok4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bi7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆠㄧ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tshiok4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ㄑㄧㆦㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ju5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆡㄨˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>si6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siong3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㆲ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ho5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄜˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>koo3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㆦ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jiok8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆢㄧㆦㆻ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ki5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄧˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hok4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㆦㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tik4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄧㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kho2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄎㄜˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>liong7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㄧㆲ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>un5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄨㄣˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>tang1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ㄉㄤˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>hong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ㄏㆲˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hi1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄧˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>khong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ㄎㆲˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hiu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄧㄨˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ia7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㄚ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>se3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㆤ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tsun1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗㄨㄣˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lam5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㆰˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>se1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ㄙㆤˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>pok4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ㄅㆦㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>siang7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ㄒㄧㄤ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ha7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄚ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ik8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㆻ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tan6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄢˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ka3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ㄍㄚ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2631,6 +2748,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="62" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
@@ -2649,9 +2769,6 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -2659,55 +2776,7 @@
     <cellStyle name="超連結" xfId="3" builtinId="8"/>
     <cellStyle name="超連結 2" xfId="2" xr:uid="{AF644068-9C78-42CD-96C0-AD9C8A3B8BDE}"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <font>
         <b/>
@@ -3380,8 +3449,8 @@
         <v>165</v>
       </c>
       <c r="C4" s="54" t="str">
-        <f xml:space="preserve"> "金剛般若波羅蜜經" &amp; TEXT(C7, "000") &amp; _xlfn.CONCAT("。", 漢字注音!D5:R5)</f>
-        <v>金剛般若波羅蜜經004。妙行無住分第四</v>
+        <f xml:space="preserve"> "金剛般若波羅蜜經" &amp; TEXT(C7, "000")</f>
+        <v>金剛般若波羅蜜經004</v>
       </c>
     </row>
     <row r="5" spans="2:3">
@@ -3404,7 +3473,7 @@
       <c r="B7" s="53" t="s">
         <v>221</v>
       </c>
-      <c r="C7" s="103">
+      <c r="C7" s="97">
         <v>4</v>
       </c>
     </row>
@@ -3500,32 +3569,32 @@
       <c r="Q3" s="83"/>
       <c r="R3" s="83"/>
       <c r="T3" s="92"/>
-      <c r="V3" s="97" t="s">
-        <v>330</v>
+      <c r="V3" s="98" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="4" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B4" s="56"/>
       <c r="D4" s="84" t="s">
-        <v>345</v>
+        <v>252</v>
       </c>
       <c r="E4" s="84" t="s">
-        <v>290</v>
+        <v>254</v>
       </c>
       <c r="F4" s="84" t="s">
-        <v>222</v>
+        <v>256</v>
       </c>
       <c r="G4" s="84" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="H4" s="84" t="s">
-        <v>224</v>
+        <v>260</v>
       </c>
       <c r="I4" s="84" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="J4" s="84" t="s">
-        <v>322</v>
+        <v>264</v>
       </c>
       <c r="K4" s="84"/>
       <c r="L4" s="84"/>
@@ -3536,17 +3605,17 @@
       <c r="Q4" s="84"/>
       <c r="R4" s="84"/>
       <c r="S4" s="93"/>
-      <c r="V4" s="98"/>
+      <c r="V4" s="99"/>
     </row>
     <row r="5" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B5" s="57">
         <v>1</v>
       </c>
       <c r="D5" s="80" t="s">
-        <v>331</v>
+        <v>238</v>
       </c>
       <c r="E5" s="80" t="s">
-        <v>313</v>
+        <v>230</v>
       </c>
       <c r="F5" s="80" t="s">
         <v>201</v>
@@ -3561,7 +3630,7 @@
         <v>169</v>
       </c>
       <c r="J5" s="80" t="s">
-        <v>321</v>
+        <v>234</v>
       </c>
       <c r="K5" s="80"/>
       <c r="L5" s="80"/>
@@ -3572,31 +3641,31 @@
       <c r="Q5" s="80"/>
       <c r="R5" s="80"/>
       <c r="S5" s="94"/>
-      <c r="V5" s="98"/>
+      <c r="V5" s="99"/>
     </row>
     <row r="6" spans="2:22" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="B6" s="58"/>
       <c r="C6" s="87"/>
       <c r="D6" s="85" t="s">
-        <v>346</v>
+        <v>253</v>
       </c>
       <c r="E6" s="85" t="s">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="F6" s="85" t="s">
-        <v>223</v>
+        <v>257</v>
       </c>
       <c r="G6" s="85" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="H6" s="85" t="s">
-        <v>225</v>
+        <v>261</v>
       </c>
       <c r="I6" s="85" t="s">
-        <v>227</v>
+        <v>263</v>
       </c>
       <c r="J6" s="85" t="s">
-        <v>323</v>
+        <v>265</v>
       </c>
       <c r="K6" s="85"/>
       <c r="L6" s="85"/>
@@ -3607,7 +3676,7 @@
       <c r="Q6" s="85"/>
       <c r="R6" s="85"/>
       <c r="S6" s="95"/>
-      <c r="V6" s="98"/>
+      <c r="V6" s="99"/>
     </row>
     <row r="7" spans="2:22" s="49" customFormat="1" ht="60" customHeight="1">
       <c r="B7" s="55"/>
@@ -3628,45 +3697,45 @@
       <c r="Q7" s="83"/>
       <c r="R7" s="83"/>
       <c r="S7" s="66"/>
-      <c r="V7" s="98"/>
+      <c r="V7" s="99"/>
     </row>
     <row r="8" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="56"/>
       <c r="D8" s="84"/>
       <c r="E8" s="84"/>
       <c r="F8" s="84" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="G8" s="84" t="s">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="H8" s="84"/>
       <c r="I8" s="84"/>
       <c r="J8" s="84" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="K8" s="84" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="L8" s="84" t="s">
-        <v>232</v>
+        <v>274</v>
       </c>
       <c r="M8" s="84"/>
       <c r="N8" s="84" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="O8" s="84" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="P8" s="84" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="Q8" s="84" t="s">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="R8" s="84"/>
       <c r="S8" s="93"/>
-      <c r="V8" s="98"/>
+      <c r="V8" s="99"/>
     </row>
     <row r="9" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B9" s="57">
@@ -3680,10 +3749,10 @@
         <v>207</v>
       </c>
       <c r="F9" s="80" t="s">
-        <v>314</v>
+        <v>231</v>
       </c>
       <c r="G9" s="80" t="s">
-        <v>315</v>
+        <v>232</v>
       </c>
       <c r="H9" s="80" t="s">
         <v>206</v>
@@ -3720,45 +3789,45 @@
       </c>
       <c r="S9" s="94"/>
       <c r="T9" s="92"/>
-      <c r="V9" s="98"/>
+      <c r="V9" s="99"/>
     </row>
     <row r="10" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="58"/>
       <c r="D10" s="85"/>
       <c r="E10" s="85"/>
       <c r="F10" s="85" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="G10" s="85" t="s">
-        <v>318</v>
+        <v>269</v>
       </c>
       <c r="H10" s="85"/>
       <c r="I10" s="85"/>
       <c r="J10" s="85" t="s">
-        <v>229</v>
+        <v>271</v>
       </c>
       <c r="K10" s="85" t="s">
-        <v>231</v>
+        <v>273</v>
       </c>
       <c r="L10" s="85" t="s">
-        <v>233</v>
+        <v>275</v>
       </c>
       <c r="M10" s="85"/>
       <c r="N10" s="85" t="s">
-        <v>231</v>
+        <v>273</v>
       </c>
       <c r="O10" s="85" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="P10" s="85" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="Q10" s="85" t="s">
-        <v>241</v>
+        <v>281</v>
       </c>
       <c r="R10" s="85"/>
       <c r="S10" s="96"/>
-      <c r="V10" s="98"/>
+      <c r="V10" s="99"/>
     </row>
     <row r="11" spans="2:22" s="66" customFormat="1" ht="60" customHeight="1">
       <c r="B11" s="65"/>
@@ -3778,53 +3847,53 @@
       <c r="P11" s="83"/>
       <c r="Q11" s="83"/>
       <c r="R11" s="83"/>
-      <c r="V11" s="98"/>
+      <c r="V11" s="99"/>
     </row>
     <row r="12" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="56"/>
       <c r="D12" s="84" t="s">
-        <v>246</v>
+        <v>282</v>
       </c>
       <c r="E12" s="84" t="s">
-        <v>222</v>
+        <v>256</v>
       </c>
       <c r="F12" s="84" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="G12" s="84" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="H12" s="84"/>
       <c r="I12" s="84" t="s">
-        <v>290</v>
+        <v>254</v>
       </c>
       <c r="J12" s="84" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="K12" s="84" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="L12" s="84" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="M12" s="84"/>
       <c r="N12" s="84" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="O12" s="84" t="s">
-        <v>311</v>
+        <v>290</v>
       </c>
       <c r="P12" s="84" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="Q12" s="84" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="R12" s="84" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="S12" s="93"/>
-      <c r="V12" s="98"/>
+      <c r="V12" s="99"/>
     </row>
     <row r="13" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B13" s="57">
@@ -3847,16 +3916,16 @@
         <v>167</v>
       </c>
       <c r="I13" s="80" t="s">
-        <v>313</v>
+        <v>230</v>
       </c>
       <c r="J13" s="80" t="s">
         <v>199</v>
       </c>
       <c r="K13" s="80" t="s">
-        <v>297</v>
+        <v>224</v>
       </c>
       <c r="L13" s="80" t="s">
-        <v>298</v>
+        <v>225</v>
       </c>
       <c r="M13" s="80" t="s">
         <v>171</v>
@@ -3865,7 +3934,7 @@
         <v>188</v>
       </c>
       <c r="O13" s="80" t="s">
-        <v>310</v>
+        <v>229</v>
       </c>
       <c r="P13" s="80" t="s">
         <v>200</v>
@@ -3874,56 +3943,56 @@
         <v>211</v>
       </c>
       <c r="R13" s="80" t="s">
-        <v>309</v>
+        <v>228</v>
       </c>
       <c r="S13" s="94"/>
-      <c r="V13" s="98"/>
+      <c r="V13" s="99"/>
     </row>
     <row r="14" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="58"/>
       <c r="D14" s="85" t="s">
-        <v>247</v>
+        <v>283</v>
       </c>
       <c r="E14" s="85" t="s">
-        <v>223</v>
+        <v>257</v>
       </c>
       <c r="F14" s="85" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="G14" s="85" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="H14" s="85"/>
       <c r="I14" s="85" t="s">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="J14" s="85" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="K14" s="85" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="L14" s="85" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="M14" s="85"/>
       <c r="N14" s="85" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="O14" s="85" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="P14" s="85" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="Q14" s="85" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="R14" s="85" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="S14" s="96"/>
-      <c r="V14" s="98"/>
+      <c r="V14" s="99"/>
     </row>
     <row r="15" spans="2:22" s="67" customFormat="1" ht="60" customHeight="1">
       <c r="B15" s="63"/>
@@ -3943,47 +4012,47 @@
       <c r="P15" s="83"/>
       <c r="Q15" s="83"/>
       <c r="R15" s="83"/>
-      <c r="V15" s="98"/>
+      <c r="V15" s="99"/>
     </row>
     <row r="16" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="56"/>
       <c r="D16" s="84" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="E16" s="84" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="F16" s="84"/>
       <c r="G16" s="84" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="H16" s="84" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="I16" s="84" t="s">
-        <v>254</v>
+        <v>296</v>
       </c>
       <c r="J16" s="84"/>
       <c r="K16" s="84" t="s">
-        <v>347</v>
+        <v>298</v>
       </c>
       <c r="L16" s="84"/>
       <c r="M16" s="84" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="N16" s="84"/>
       <c r="O16" s="84" t="s">
-        <v>349</v>
+        <v>302</v>
       </c>
       <c r="P16" s="84"/>
       <c r="Q16" s="84" t="s">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="R16" s="84" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="S16" s="93"/>
-      <c r="V16" s="98"/>
+      <c r="V16" s="99"/>
     </row>
     <row r="17" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B17" s="57">
@@ -3991,10 +4060,10 @@
         <v>4</v>
       </c>
       <c r="D17" s="80" t="s">
-        <v>297</v>
+        <v>224</v>
       </c>
       <c r="E17" s="80" t="s">
-        <v>298</v>
+        <v>225</v>
       </c>
       <c r="F17" s="80" t="s">
         <v>167</v>
@@ -4006,25 +4075,25 @@
         <v>211</v>
       </c>
       <c r="I17" s="80" t="s">
-        <v>324</v>
+        <v>235</v>
       </c>
       <c r="J17" s="80" t="s">
         <v>195</v>
       </c>
       <c r="K17" s="80" t="s">
-        <v>332</v>
+        <v>239</v>
       </c>
       <c r="L17" s="80" t="s">
         <v>195</v>
       </c>
       <c r="M17" s="80" t="s">
-        <v>333</v>
+        <v>240</v>
       </c>
       <c r="N17" s="80" t="s">
         <v>195</v>
       </c>
       <c r="O17" s="80" t="s">
-        <v>334</v>
+        <v>241</v>
       </c>
       <c r="P17" s="80" t="s">
         <v>195</v>
@@ -4033,50 +4102,50 @@
         <v>217</v>
       </c>
       <c r="R17" s="80" t="s">
-        <v>297</v>
+        <v>224</v>
       </c>
       <c r="S17" s="94"/>
-      <c r="V17" s="98"/>
+      <c r="V17" s="99"/>
     </row>
     <row r="18" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="58"/>
       <c r="D18" s="85" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="E18" s="85" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="F18" s="85"/>
       <c r="G18" s="85" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="H18" s="85" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="I18" s="85" t="s">
-        <v>255</v>
+        <v>297</v>
       </c>
       <c r="J18" s="85"/>
       <c r="K18" s="85" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="L18" s="85"/>
       <c r="M18" s="85" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="N18" s="85"/>
       <c r="O18" s="85" t="s">
-        <v>350</v>
+        <v>303</v>
       </c>
       <c r="P18" s="85"/>
       <c r="Q18" s="85" t="s">
-        <v>241</v>
+        <v>281</v>
       </c>
       <c r="R18" s="85" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="S18" s="96"/>
-      <c r="V18" s="98"/>
+      <c r="V18" s="99"/>
     </row>
     <row r="19" spans="2:22" s="67" customFormat="1" ht="60" customHeight="1">
       <c r="B19" s="63"/>
@@ -4096,51 +4165,51 @@
       <c r="P19" s="83"/>
       <c r="Q19" s="83"/>
       <c r="R19" s="83"/>
-      <c r="V19" s="98"/>
+      <c r="V19" s="99"/>
     </row>
     <row r="20" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B20" s="56"/>
       <c r="D20" s="84" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="E20" s="84"/>
       <c r="F20" s="84" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="G20" s="84" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="H20" s="84" t="s">
-        <v>232</v>
+        <v>274</v>
       </c>
       <c r="I20" s="84"/>
       <c r="J20" s="84" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="K20" s="84" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="L20" s="84" t="s">
-        <v>246</v>
+        <v>282</v>
       </c>
       <c r="M20" s="84" t="s">
-        <v>256</v>
+        <v>304</v>
       </c>
       <c r="N20" s="84" t="s">
-        <v>258</v>
+        <v>306</v>
       </c>
       <c r="O20" s="84" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="P20" s="84" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="Q20" s="84"/>
       <c r="R20" s="84" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="S20" s="93"/>
-      <c r="V20" s="98"/>
+      <c r="V20" s="99"/>
     </row>
     <row r="21" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B21" s="57">
@@ -4148,7 +4217,7 @@
         <v>5</v>
       </c>
       <c r="D21" s="80" t="s">
-        <v>298</v>
+        <v>225</v>
       </c>
       <c r="E21" s="80" t="s">
         <v>171</v>
@@ -4181,10 +4250,10 @@
         <v>170</v>
       </c>
       <c r="O21" s="80" t="s">
-        <v>297</v>
+        <v>224</v>
       </c>
       <c r="P21" s="80" t="s">
-        <v>298</v>
+        <v>225</v>
       </c>
       <c r="Q21" s="80" t="s">
         <v>167</v>
@@ -4193,51 +4262,51 @@
         <v>200</v>
       </c>
       <c r="S21" s="94"/>
-      <c r="V21" s="98"/>
+      <c r="V21" s="99"/>
     </row>
     <row r="22" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="58"/>
       <c r="D22" s="85" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="E22" s="85"/>
       <c r="F22" s="85" t="s">
-        <v>229</v>
+        <v>271</v>
       </c>
       <c r="G22" s="85" t="s">
-        <v>231</v>
+        <v>273</v>
       </c>
       <c r="H22" s="85" t="s">
-        <v>233</v>
+        <v>275</v>
       </c>
       <c r="I22" s="85"/>
       <c r="J22" s="85" t="s">
-        <v>231</v>
+        <v>273</v>
       </c>
       <c r="K22" s="85" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="L22" s="85" t="s">
-        <v>247</v>
+        <v>283</v>
       </c>
       <c r="M22" s="85" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="N22" s="85" t="s">
-        <v>259</v>
+        <v>307</v>
       </c>
       <c r="O22" s="85" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="P22" s="85" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="Q22" s="85"/>
       <c r="R22" s="85" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="S22" s="96"/>
-      <c r="V22" s="99"/>
+      <c r="V22" s="100"/>
     </row>
     <row r="23" spans="2:22" s="67" customFormat="1" ht="60" customHeight="1">
       <c r="B23" s="63"/>
@@ -4262,45 +4331,45 @@
     <row r="24" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B24" s="56"/>
       <c r="D24" s="84" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="E24" s="84" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="F24" s="84" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="G24" s="84"/>
       <c r="H24" s="84" t="s">
-        <v>244</v>
+        <v>310</v>
       </c>
       <c r="I24" s="84" t="s">
-        <v>260</v>
+        <v>312</v>
       </c>
       <c r="J24" s="84" t="s">
-        <v>262</v>
+        <v>314</v>
       </c>
       <c r="K24" s="84"/>
       <c r="L24" s="84" t="s">
-        <v>264</v>
+        <v>316</v>
       </c>
       <c r="M24" s="84" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="N24" s="84" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="O24" s="84" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="P24" s="84" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="Q24" s="84" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="R24" s="84" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="S24" s="93"/>
       <c r="V24" s="60"/>
@@ -4353,7 +4422,7 @@
         <v>216</v>
       </c>
       <c r="R25" s="80" t="s">
-        <v>297</v>
+        <v>224</v>
       </c>
       <c r="S25" s="94"/>
       <c r="V25" s="60"/>
@@ -4361,45 +4430,45 @@
     <row r="26" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B26" s="58"/>
       <c r="D26" s="85" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="E26" s="85" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="F26" s="85" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="G26" s="85"/>
       <c r="H26" s="85" t="s">
-        <v>245</v>
+        <v>311</v>
       </c>
       <c r="I26" s="85" t="s">
-        <v>261</v>
+        <v>313</v>
       </c>
       <c r="J26" s="85" t="s">
-        <v>263</v>
+        <v>315</v>
       </c>
       <c r="K26" s="85"/>
       <c r="L26" s="85" t="s">
-        <v>265</v>
+        <v>317</v>
       </c>
       <c r="M26" s="85" t="s">
-        <v>231</v>
+        <v>273</v>
       </c>
       <c r="N26" s="85" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="O26" s="85" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="P26" s="85" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="Q26" s="85" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="R26" s="85" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="S26" s="96"/>
       <c r="U26" s="1" t="str">
@@ -4435,43 +4504,43 @@
     <row r="28" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B28" s="56"/>
       <c r="D28" s="84" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="E28" s="84"/>
       <c r="F28" s="84" t="s">
-        <v>252</v>
+        <v>318</v>
       </c>
       <c r="G28" s="84" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="H28" s="84" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="I28" s="84" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="J28" s="84" t="s">
-        <v>292</v>
+        <v>324</v>
       </c>
       <c r="K28" s="84" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="L28" s="84" t="s">
-        <v>286</v>
+        <v>326</v>
       </c>
       <c r="M28" s="84"/>
       <c r="N28" s="84" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="O28" s="84" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="P28" s="84" t="s">
-        <v>232</v>
+        <v>274</v>
       </c>
       <c r="Q28" s="84"/>
       <c r="R28" s="84" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="S28" s="93"/>
       <c r="U28" s="67" t="str">
@@ -4486,7 +4555,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="80" t="s">
-        <v>298</v>
+        <v>225</v>
       </c>
       <c r="E29" s="80" t="s">
         <v>167</v>
@@ -4495,19 +4564,19 @@
         <v>213</v>
       </c>
       <c r="G29" s="80" t="s">
-        <v>299</v>
+        <v>226</v>
       </c>
       <c r="H29" s="80" t="s">
-        <v>300</v>
+        <v>227</v>
       </c>
       <c r="I29" s="80" t="s">
         <v>200</v>
       </c>
       <c r="J29" s="80" t="s">
-        <v>289</v>
+        <v>223</v>
       </c>
       <c r="K29" s="80" t="s">
-        <v>335</v>
+        <v>242</v>
       </c>
       <c r="L29" s="80" t="s">
         <v>205</v>
@@ -4540,43 +4609,43 @@
     <row r="30" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B30" s="58"/>
       <c r="D30" s="85" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="E30" s="85"/>
       <c r="F30" s="85" t="s">
-        <v>253</v>
+        <v>319</v>
       </c>
       <c r="G30" s="85" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="H30" s="85" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="I30" s="85" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="J30" s="85" t="s">
-        <v>293</v>
+        <v>325</v>
       </c>
       <c r="K30" s="85" t="s">
-        <v>229</v>
+        <v>271</v>
       </c>
       <c r="L30" s="85" t="s">
-        <v>287</v>
+        <v>327</v>
       </c>
       <c r="M30" s="85"/>
       <c r="N30" s="85" t="s">
-        <v>229</v>
+        <v>271</v>
       </c>
       <c r="O30" s="85" t="s">
-        <v>231</v>
+        <v>273</v>
       </c>
       <c r="P30" s="85" t="s">
-        <v>233</v>
+        <v>275</v>
       </c>
       <c r="Q30" s="85"/>
       <c r="R30" s="85" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="S30" s="96"/>
       <c r="U30" s="67" t="str">
@@ -4600,7 +4669,7 @@
       <c r="M31" s="83"/>
       <c r="N31" s="83"/>
       <c r="O31" s="83" t="s">
-        <v>288</v>
+        <v>222</v>
       </c>
       <c r="P31" s="83"/>
       <c r="Q31" s="83"/>
@@ -4614,38 +4683,38 @@
     <row r="32" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B32" s="56"/>
       <c r="D32" s="84" t="s">
-        <v>274</v>
+        <v>328</v>
       </c>
       <c r="E32" s="84" t="s">
-        <v>242</v>
+        <v>330</v>
       </c>
       <c r="F32" s="84" t="s">
-        <v>244</v>
+        <v>310</v>
       </c>
       <c r="G32" s="84"/>
       <c r="H32" s="84" t="s">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="I32" s="84" t="s">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="J32" s="84" t="s">
-        <v>282</v>
+        <v>336</v>
       </c>
       <c r="K32" s="84" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="L32" s="84" t="s">
-        <v>292</v>
+        <v>324</v>
       </c>
       <c r="M32" s="84" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="N32" s="84" t="s">
-        <v>286</v>
+        <v>326</v>
       </c>
       <c r="O32" s="84" t="s">
-        <v>288</v>
+        <v>340</v>
       </c>
       <c r="P32" s="84"/>
       <c r="Q32" s="84"/>
@@ -4675,22 +4744,22 @@
         <v>212</v>
       </c>
       <c r="H33" s="80" t="s">
-        <v>336</v>
+        <v>243</v>
       </c>
       <c r="I33" s="80" t="s">
-        <v>337</v>
+        <v>244</v>
       </c>
       <c r="J33" s="80" t="s">
         <v>220</v>
       </c>
       <c r="K33" s="80" t="s">
-        <v>338</v>
+        <v>245</v>
       </c>
       <c r="L33" s="80" t="s">
-        <v>289</v>
+        <v>223</v>
       </c>
       <c r="M33" s="80" t="s">
-        <v>335</v>
+        <v>242</v>
       </c>
       <c r="N33" s="80" t="s">
         <v>205</v>
@@ -4713,38 +4782,38 @@
     <row r="34" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B34" s="58"/>
       <c r="D34" s="85" t="s">
-        <v>275</v>
+        <v>329</v>
       </c>
       <c r="E34" s="85" t="s">
-        <v>243</v>
+        <v>331</v>
       </c>
       <c r="F34" s="85" t="s">
-        <v>245</v>
+        <v>311</v>
       </c>
       <c r="G34" s="85"/>
       <c r="H34" s="85" t="s">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="I34" s="85" t="s">
-        <v>354</v>
+        <v>335</v>
       </c>
       <c r="J34" s="85" t="s">
-        <v>283</v>
+        <v>337</v>
       </c>
       <c r="K34" s="85" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="L34" s="85" t="s">
-        <v>293</v>
+        <v>325</v>
       </c>
       <c r="M34" s="85" t="s">
-        <v>229</v>
+        <v>271</v>
       </c>
       <c r="N34" s="85" t="s">
-        <v>287</v>
+        <v>327</v>
       </c>
       <c r="O34" s="85" t="s">
-        <v>296</v>
+        <v>341</v>
       </c>
       <c r="P34" s="85"/>
       <c r="Q34" s="85"/>
@@ -4775,37 +4844,37 @@
     <row r="36" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B36" s="56"/>
       <c r="D36" s="84" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="E36" s="84" t="s">
-        <v>278</v>
+        <v>342</v>
       </c>
       <c r="F36" s="84"/>
       <c r="G36" s="84" t="s">
-        <v>234</v>
+        <v>344</v>
       </c>
       <c r="H36" s="84" t="s">
-        <v>236</v>
+        <v>346</v>
       </c>
       <c r="I36" s="84"/>
       <c r="J36" s="84"/>
       <c r="K36" s="84"/>
       <c r="L36" s="84" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="M36" s="84" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="N36" s="84" t="s">
-        <v>232</v>
+        <v>274</v>
       </c>
       <c r="O36" s="84"/>
       <c r="P36" s="84" t="s">
-        <v>238</v>
+        <v>348</v>
       </c>
       <c r="Q36" s="84"/>
       <c r="R36" s="84" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="S36" s="93"/>
       <c r="V36" s="60"/>
@@ -4852,13 +4921,13 @@
         <v>186</v>
       </c>
       <c r="P37" s="80" t="s">
-        <v>339</v>
+        <v>246</v>
       </c>
       <c r="Q37" s="80" t="s">
         <v>195</v>
       </c>
       <c r="R37" s="80" t="s">
-        <v>340</v>
+        <v>247</v>
       </c>
       <c r="S37" s="94"/>
       <c r="V37" s="60"/>
@@ -4866,37 +4935,37 @@
     <row r="38" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B38" s="58"/>
       <c r="D38" s="85" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="E38" s="85" t="s">
-        <v>279</v>
+        <v>343</v>
       </c>
       <c r="F38" s="85"/>
       <c r="G38" s="85" t="s">
-        <v>235</v>
+        <v>345</v>
       </c>
       <c r="H38" s="85" t="s">
-        <v>237</v>
+        <v>347</v>
       </c>
       <c r="I38" s="85"/>
       <c r="J38" s="85"/>
       <c r="K38" s="85"/>
       <c r="L38" s="85" t="s">
-        <v>229</v>
+        <v>271</v>
       </c>
       <c r="M38" s="85" t="s">
-        <v>231</v>
+        <v>273</v>
       </c>
       <c r="N38" s="85" t="s">
-        <v>233</v>
+        <v>275</v>
       </c>
       <c r="O38" s="85"/>
       <c r="P38" s="85" t="s">
-        <v>239</v>
+        <v>349</v>
       </c>
       <c r="Q38" s="85"/>
       <c r="R38" s="85" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="S38" s="96"/>
       <c r="V38" s="60"/>
@@ -4925,38 +4994,38 @@
       <c r="B40" s="56"/>
       <c r="D40" s="84"/>
       <c r="E40" s="84" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="F40" s="84" t="s">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="G40" s="84"/>
       <c r="H40" s="84" t="s">
-        <v>322</v>
+        <v>264</v>
       </c>
       <c r="I40" s="84" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="J40" s="84"/>
       <c r="K40" s="84" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="L40" s="84"/>
       <c r="M40" s="84" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="N40" s="84" t="s">
-        <v>282</v>
+        <v>336</v>
       </c>
       <c r="O40" s="84" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="P40" s="84"/>
       <c r="Q40" s="84" t="s">
-        <v>292</v>
+        <v>324</v>
       </c>
       <c r="R40" s="84" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="S40" s="93"/>
       <c r="V40" s="60"/>
@@ -4970,46 +5039,46 @@
         <v>195</v>
       </c>
       <c r="E41" s="80" t="s">
-        <v>341</v>
+        <v>248</v>
       </c>
       <c r="F41" s="80" t="s">
-        <v>337</v>
+        <v>244</v>
       </c>
       <c r="G41" s="80" t="s">
         <v>195</v>
       </c>
       <c r="H41" s="80" t="s">
-        <v>321</v>
+        <v>234</v>
       </c>
       <c r="I41" s="80" t="s">
-        <v>342</v>
+        <v>249</v>
       </c>
       <c r="J41" s="80" t="s">
         <v>195</v>
       </c>
       <c r="K41" s="80" t="s">
-        <v>343</v>
+        <v>250</v>
       </c>
       <c r="L41" s="80" t="s">
         <v>195</v>
       </c>
       <c r="M41" s="80" t="s">
-        <v>316</v>
+        <v>233</v>
       </c>
       <c r="N41" s="80" t="s">
         <v>220</v>
       </c>
       <c r="O41" s="80" t="s">
-        <v>338</v>
+        <v>245</v>
       </c>
       <c r="P41" s="80" t="s">
         <v>167</v>
       </c>
       <c r="Q41" s="80" t="s">
-        <v>289</v>
+        <v>223</v>
       </c>
       <c r="R41" s="80" t="s">
-        <v>335</v>
+        <v>242</v>
       </c>
       <c r="S41" s="94"/>
       <c r="V41" s="60"/>
@@ -5018,38 +5087,38 @@
       <c r="B42" s="58"/>
       <c r="D42" s="85"/>
       <c r="E42" s="85" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="F42" s="85" t="s">
-        <v>354</v>
+        <v>335</v>
       </c>
       <c r="G42" s="85"/>
       <c r="H42" s="85" t="s">
-        <v>323</v>
+        <v>265</v>
       </c>
       <c r="I42" s="85" t="s">
-        <v>329</v>
+        <v>355</v>
       </c>
       <c r="J42" s="85"/>
       <c r="K42" s="85" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="L42" s="85"/>
       <c r="M42" s="85" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="N42" s="85" t="s">
-        <v>283</v>
+        <v>337</v>
       </c>
       <c r="O42" s="85" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="P42" s="85"/>
       <c r="Q42" s="85" t="s">
-        <v>293</v>
+        <v>325</v>
       </c>
       <c r="R42" s="85" t="s">
-        <v>229</v>
+        <v>271</v>
       </c>
       <c r="S42" s="96"/>
       <c r="V42" s="60"/>
@@ -5059,7 +5128,7 @@
       <c r="C43" s="90"/>
       <c r="D43" s="83"/>
       <c r="E43" s="83" t="s">
-        <v>288</v>
+        <v>222</v>
       </c>
       <c r="F43" s="83"/>
       <c r="G43" s="83"/>
@@ -5079,35 +5148,35 @@
     <row r="44" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B44" s="56"/>
       <c r="D44" s="84" t="s">
-        <v>286</v>
+        <v>326</v>
       </c>
       <c r="E44" s="84" t="s">
-        <v>288</v>
+        <v>340</v>
       </c>
       <c r="F44" s="84"/>
       <c r="G44" s="84"/>
       <c r="H44" s="84"/>
       <c r="I44" s="84" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="J44" s="84" t="s">
-        <v>278</v>
+        <v>342</v>
       </c>
       <c r="K44" s="84"/>
       <c r="L44" s="84" t="s">
-        <v>234</v>
+        <v>344</v>
       </c>
       <c r="M44" s="84" t="s">
-        <v>236</v>
+        <v>346</v>
       </c>
       <c r="N44" s="84"/>
       <c r="O44" s="84"/>
       <c r="P44" s="84"/>
       <c r="Q44" s="84" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="R44" s="84" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="S44" s="93"/>
       <c r="V44" s="60"/>
@@ -5168,35 +5237,35 @@
     <row r="46" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B46" s="58"/>
       <c r="D46" s="85" t="s">
-        <v>287</v>
+        <v>327</v>
       </c>
       <c r="E46" s="85" t="s">
-        <v>296</v>
+        <v>341</v>
       </c>
       <c r="F46" s="85"/>
       <c r="G46" s="85"/>
       <c r="H46" s="85"/>
       <c r="I46" s="85" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="J46" s="85" t="s">
-        <v>279</v>
+        <v>343</v>
       </c>
       <c r="K46" s="85"/>
       <c r="L46" s="85" t="s">
-        <v>235</v>
+        <v>345</v>
       </c>
       <c r="M46" s="85" t="s">
-        <v>237</v>
+        <v>347</v>
       </c>
       <c r="N46" s="85"/>
       <c r="O46" s="85"/>
       <c r="P46" s="85"/>
       <c r="Q46" s="85" t="s">
-        <v>229</v>
+        <v>271</v>
       </c>
       <c r="R46" s="85" t="s">
-        <v>231</v>
+        <v>273</v>
       </c>
       <c r="S46" s="96"/>
       <c r="V46" s="60"/>
@@ -5224,45 +5293,45 @@
     <row r="48" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B48" s="56"/>
       <c r="D48" s="84" t="s">
-        <v>232</v>
+        <v>274</v>
       </c>
       <c r="E48" s="84"/>
       <c r="F48" s="84" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="G48" s="84" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="H48" s="84" t="s">
-        <v>222</v>
+        <v>256</v>
       </c>
       <c r="I48" s="84" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="J48" s="84" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="K48" s="84" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="L48" s="84" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="M48" s="84"/>
       <c r="N48" s="84" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="O48" s="84" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="P48" s="84" t="s">
-        <v>284</v>
+        <v>360</v>
       </c>
       <c r="Q48" s="84" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="R48" s="84" t="s">
-        <v>256</v>
+        <v>304</v>
       </c>
       <c r="S48" s="93"/>
       <c r="V48" s="60"/>
@@ -5294,25 +5363,25 @@
         <v>216</v>
       </c>
       <c r="K49" s="80" t="s">
-        <v>297</v>
+        <v>224</v>
       </c>
       <c r="L49" s="80" t="s">
-        <v>298</v>
+        <v>225</v>
       </c>
       <c r="M49" s="80" t="s">
         <v>167</v>
       </c>
       <c r="N49" s="80" t="s">
-        <v>299</v>
+        <v>226</v>
       </c>
       <c r="O49" s="80" t="s">
-        <v>300</v>
+        <v>227</v>
       </c>
       <c r="P49" s="80" t="s">
         <v>204</v>
       </c>
       <c r="Q49" s="80" t="s">
-        <v>314</v>
+        <v>231</v>
       </c>
       <c r="R49" s="80" t="s">
         <v>214</v>
@@ -5323,45 +5392,45 @@
     <row r="50" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B50" s="58"/>
       <c r="D50" s="85" t="s">
-        <v>233</v>
+        <v>275</v>
       </c>
       <c r="E50" s="85"/>
       <c r="F50" s="85" t="s">
-        <v>231</v>
+        <v>273</v>
       </c>
       <c r="G50" s="85" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="H50" s="85" t="s">
-        <v>223</v>
+        <v>257</v>
       </c>
       <c r="I50" s="85" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="J50" s="85" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="K50" s="85" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="L50" s="85" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="M50" s="85"/>
       <c r="N50" s="85" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="O50" s="85" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="P50" s="85" t="s">
-        <v>285</v>
+        <v>361</v>
       </c>
       <c r="Q50" s="85" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="R50" s="85" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="S50" s="96"/>
       <c r="V50" s="60"/>
@@ -5389,45 +5458,45 @@
     <row r="52" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B52" s="56"/>
       <c r="D52" s="84" t="s">
-        <v>258</v>
+        <v>306</v>
       </c>
       <c r="E52" s="84" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="F52" s="84" t="s">
-        <v>292</v>
+        <v>324</v>
       </c>
       <c r="G52" s="84" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="H52" s="84" t="s">
-        <v>286</v>
+        <v>326</v>
       </c>
       <c r="I52" s="84"/>
       <c r="J52" s="84" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="K52" s="84" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="L52" s="84" t="s">
-        <v>232</v>
+        <v>274</v>
       </c>
       <c r="M52" s="84"/>
       <c r="N52" s="84" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="O52" s="84" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="P52" s="84" t="s">
-        <v>326</v>
+        <v>362</v>
       </c>
       <c r="Q52" s="84" t="s">
-        <v>246</v>
+        <v>282</v>
       </c>
       <c r="R52" s="84" t="s">
-        <v>256</v>
+        <v>304</v>
       </c>
       <c r="S52" s="93"/>
       <c r="V52" s="60"/>
@@ -5444,10 +5513,10 @@
         <v>200</v>
       </c>
       <c r="F53" s="80" t="s">
-        <v>289</v>
+        <v>223</v>
       </c>
       <c r="G53" s="81" t="s">
-        <v>335</v>
+        <v>242</v>
       </c>
       <c r="H53" s="81" t="s">
         <v>205</v>
@@ -5474,7 +5543,7 @@
         <v>215</v>
       </c>
       <c r="P53" s="80" t="s">
-        <v>325</v>
+        <v>236</v>
       </c>
       <c r="Q53" s="80" t="s">
         <v>203</v>
@@ -5488,45 +5557,45 @@
     <row r="54" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B54" s="58"/>
       <c r="D54" s="85" t="s">
-        <v>259</v>
+        <v>307</v>
       </c>
       <c r="E54" s="85" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="F54" s="85" t="s">
-        <v>293</v>
+        <v>325</v>
       </c>
       <c r="G54" s="85" t="s">
-        <v>229</v>
+        <v>271</v>
       </c>
       <c r="H54" s="85" t="s">
-        <v>287</v>
+        <v>327</v>
       </c>
       <c r="I54" s="85"/>
       <c r="J54" s="85" t="s">
-        <v>229</v>
+        <v>271</v>
       </c>
       <c r="K54" s="85" t="s">
-        <v>231</v>
+        <v>273</v>
       </c>
       <c r="L54" s="85" t="s">
-        <v>233</v>
+        <v>275</v>
       </c>
       <c r="M54" s="85"/>
       <c r="N54" s="85" t="s">
-        <v>231</v>
+        <v>273</v>
       </c>
       <c r="O54" s="85" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="P54" s="85" t="s">
-        <v>327</v>
+        <v>363</v>
       </c>
       <c r="Q54" s="85" t="s">
-        <v>247</v>
+        <v>283</v>
       </c>
       <c r="R54" s="85" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="S54" s="96"/>
       <c r="V54" s="60"/>
@@ -5554,13 +5623,13 @@
     <row r="56" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B56" s="56"/>
       <c r="D56" s="84" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="E56" s="84" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F56" s="84" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="G56" s="84"/>
       <c r="H56" s="84"/>
@@ -5586,7 +5655,7 @@
         <v>188</v>
       </c>
       <c r="E57" s="80" t="s">
-        <v>344</v>
+        <v>251</v>
       </c>
       <c r="F57" s="80" t="s">
         <v>211</v>
@@ -5613,13 +5682,13 @@
     <row r="58" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B58" s="58"/>
       <c r="D58" s="85" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="E58" s="85" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F58" s="85" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="G58" s="85"/>
       <c r="H58" s="85"/>
@@ -9384,26 +9453,26 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="D3:R3">
-    <cfRule type="expression" dxfId="13" priority="363">
+    <cfRule type="expression" dxfId="9" priority="363">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="364">
+    <cfRule type="expression" dxfId="8" priority="364">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:R7 D11:R11 D15:R15 D23:R23 D31:R31 D39:R39 D47:R47 D51:R51 D59:R59 D63:R63 D67:R67 D75:R75 D79:R79 D83:R83 D87:R87 D91:R91 D95:R95 D99:R99 D103:R103 D107:R107 D111:R111 D115:R115 D119:R119 D123:R123 D127:R127 D131:R131 D135:R135 D139:R139 D143:R143 D147:R147 D151:R151 D155:R155 D159:R159 D163:R163 D19:R19 D27:R27 D35:R35 D43:R43 D55:R55 D71:R71">
-    <cfRule type="expression" dxfId="11" priority="7">
+  <conditionalFormatting sqref="D7:R7 D11:R11 D15:R15 D19:R19 D23:R23 D27:R27 D31:R31 D35:R35 D39:R39 D43:R43 D47:R47 D51:R51 D55:R55 D59:R59 D63:R63 D67:R67 D71:R71 D75:R75 D79:R79 D83:R83 D87:R87 D91:R91 D95:R95 D99:R99 D103:R103 D107:R107 D111:R111 D115:R115 D119:R119 D123:R123 D127:R127 D131:R131 D135:R135 D139:R139 D143:R143 D147:R147 D151:R151 D155:R155 D159:R159 D163:R163">
+    <cfRule type="expression" dxfId="7" priority="7">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="8">
+    <cfRule type="expression" dxfId="6" priority="8">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D167:R167 D171:R171 D175:R175 D179:R179 D183:R183 D187:R187 D191:R191 D195:R195 D199:R199">
-    <cfRule type="expression" dxfId="9" priority="5">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="6">
+    <cfRule type="expression" dxfId="4" priority="6">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9480,7 +9549,7 @@
       </c>
     </row>
     <row r="5" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B5" s="100" t="s">
+      <c r="B5" s="101" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
@@ -9498,7 +9567,7 @@
       <c r="G5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="100" t="s">
+      <c r="I5" s="101" t="s">
         <v>6</v>
       </c>
       <c r="J5" s="6" t="s">
@@ -9523,7 +9592,7 @@
       <c r="R5" s="10"/>
     </row>
     <row r="6" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B6" s="101"/>
+      <c r="B6" s="102"/>
       <c r="C6" s="11" t="s">
         <v>16</v>
       </c>
@@ -9543,7 +9612,7 @@
         <f>$B5 &amp; G$4</f>
         <v>陰入</v>
       </c>
-      <c r="I6" s="101"/>
+      <c r="I6" s="102"/>
       <c r="J6" s="11" t="s">
         <v>17</v>
       </c>
@@ -9565,7 +9634,7 @@
       <c r="Q6" s="14"/>
     </row>
     <row r="7" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B7" s="101"/>
+      <c r="B7" s="102"/>
       <c r="C7" s="15" t="s">
         <v>22</v>
       </c>
@@ -9581,7 +9650,7 @@
       <c r="G7" s="16">
         <v>30</v>
       </c>
-      <c r="I7" s="101"/>
+      <c r="I7" s="102"/>
       <c r="J7" s="15" t="s">
         <v>22</v>
       </c>
@@ -9603,7 +9672,7 @@
       <c r="Q7" s="14"/>
     </row>
     <row r="8" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B8" s="101"/>
+      <c r="B8" s="102"/>
       <c r="C8" s="11" t="s">
         <v>24</v>
       </c>
@@ -9619,7 +9688,7 @@
       <c r="G8" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="101"/>
+      <c r="I8" s="102"/>
       <c r="J8" s="18" t="s">
         <v>24</v>
       </c>
@@ -9641,7 +9710,7 @@
       <c r="Q8" s="14"/>
     </row>
     <row r="9" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B9" s="101"/>
+      <c r="B9" s="102"/>
       <c r="C9" s="11" t="s">
         <v>33</v>
       </c>
@@ -9657,7 +9726,7 @@
       <c r="G9" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="I9" s="101"/>
+      <c r="I9" s="102"/>
       <c r="J9" s="11" t="s">
         <v>33</v>
       </c>
@@ -9679,7 +9748,7 @@
       <c r="Q9" s="14"/>
     </row>
     <row r="10" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B10" s="102"/>
+      <c r="B10" s="103"/>
       <c r="C10" s="11" t="s">
         <v>38</v>
       </c>
@@ -9695,7 +9764,7 @@
       <c r="G10" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="I10" s="102"/>
+      <c r="I10" s="103"/>
       <c r="J10" s="11" t="s">
         <v>43</v>
       </c>
@@ -9718,7 +9787,7 @@
       <c r="R10" s="28"/>
     </row>
     <row r="11" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B11" s="100" t="s">
+      <c r="B11" s="101" t="s">
         <v>48</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -9736,7 +9805,7 @@
       <c r="G11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="I11" s="100" t="s">
+      <c r="I11" s="101" t="s">
         <v>48</v>
       </c>
       <c r="J11" s="6" t="s">
@@ -9760,7 +9829,7 @@
       <c r="Q11" s="14"/>
     </row>
     <row r="12" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B12" s="101"/>
+      <c r="B12" s="102"/>
       <c r="C12" s="11" t="s">
         <v>16</v>
       </c>
@@ -9780,7 +9849,7 @@
         <f>$B11 &amp; G$4</f>
         <v>陽入</v>
       </c>
-      <c r="I12" s="101"/>
+      <c r="I12" s="102"/>
       <c r="J12" s="11" t="s">
         <v>17</v>
       </c>
@@ -9800,7 +9869,7 @@
       <c r="Q12" s="14"/>
     </row>
     <row r="13" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B13" s="101"/>
+      <c r="B13" s="102"/>
       <c r="C13" s="15" t="s">
         <v>22</v>
       </c>
@@ -9814,7 +9883,7 @@
       <c r="G13" s="16">
         <v>50</v>
       </c>
-      <c r="I13" s="101"/>
+      <c r="I13" s="102"/>
       <c r="J13" s="15" t="s">
         <v>22</v>
       </c>
@@ -9834,7 +9903,7 @@
       <c r="Q13" s="14"/>
     </row>
     <row r="14" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B14" s="101"/>
+      <c r="B14" s="102"/>
       <c r="C14" s="11" t="s">
         <v>24</v>
       </c>
@@ -9848,7 +9917,7 @@
       <c r="G14" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="I14" s="101"/>
+      <c r="I14" s="102"/>
       <c r="J14" s="11" t="s">
         <v>24</v>
       </c>
@@ -9868,7 +9937,7 @@
       <c r="Q14" s="14"/>
     </row>
     <row r="15" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B15" s="101"/>
+      <c r="B15" s="102"/>
       <c r="C15" s="11" t="s">
         <v>33</v>
       </c>
@@ -9882,7 +9951,7 @@
       <c r="G15" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="I15" s="101"/>
+      <c r="I15" s="102"/>
       <c r="J15" s="11" t="s">
         <v>33</v>
       </c>
@@ -9902,7 +9971,7 @@
       <c r="Q15" s="14"/>
     </row>
     <row r="16" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B16" s="102"/>
+      <c r="B16" s="103"/>
       <c r="C16" s="11" t="s">
         <v>38</v>
       </c>
@@ -9916,7 +9985,7 @@
       <c r="G16" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="I16" s="102"/>
+      <c r="I16" s="103"/>
       <c r="J16" s="11" t="s">
         <v>43</v>
       </c>
